--- a/src/CQs.xlsx
+++ b/src/CQs.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3DE00F-338B-46AC-AA4E-450865B992C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205459D2-EB56-4B40-8CB5-F7A53769E709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28665" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CQs" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CQs!$A$1:$G$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CQs!$C$1:$C$154</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="598">
   <si>
     <t>CQ</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>Which character archetypes appear in more than three works in the corpus?</t>
-  </si>
-  <si>
-    <t>Which works in the corpus were published before 1900?</t>
   </si>
   <si>
     <t>dcterms:issued</t>
@@ -154,9 +151,6 @@
   ?work a lrm:F1_Work ;
         gc:GP0_has_feature sf:Feature_third_person_narrator .
 }</t>
-  </si>
-  <si>
-    <t>Which character archetypes appear most frequently in a "dystopia" setting?</t>
   </si>
   <si>
     <t>SELECT ?author 
@@ -405,14 +399,6 @@
       </rPr>
       <t>?</t>
     </r>
-  </si>
-  <si>
-    <t>SELECT ?org ?label ?type WHERE {   
-  ?org a dul:Organization ;        
-         crm:P67i_is_referred_to_by sf:LHomme_Bicycle_Work ;        
-         rdfs:label ?label .   
-  OPTIONAL { ?org crm:P2_has_type ?type . } 
-}</t>
   </si>
   <si>
     <t>SELECT ?community ?label (COUNT(?member) AS ?nb) WHERE {   
@@ -720,9 +706,6 @@
     </r>
   </si>
   <si>
-    <t>Which characters play a protagonist role?</t>
-  </si>
-  <si>
     <t>SELECT DISTINCT ?event ?label WHERE {
   ?nu a gc:G9_Narrative_Unit ;
       dolce:proper-part-of sf:LHomme_Bicycle_Work ;
@@ -813,9 +796,6 @@
     <t>Which novums appear in more than one work?</t>
   </si>
   <si>
-    <t>Which types are shared by more than three works in the corpus?</t>
-  </si>
-  <si>
     <t>SELECT ?type (COUNT(DISTINCT ?work) AS ?nb_works) WHERE {
   ?work a lrm:F1_Work ;         
         crm:P2_has_type ?type . 
@@ -901,9 +881,6 @@
   </si>
   <si>
     <t>revoir la façon dont les relations sont conceptualisées</t>
-  </si>
-  <si>
-    <t>Which motifs are exclusively associated with a given thematic type such as "Dystopia"?</t>
   </si>
   <si>
     <t>SELECT DISTINCT ?motif ?label WHERE {   
@@ -922,9 +899,6 @@
 }</t>
   </si>
   <si>
-    <t>Which narrative motifs are most frequent between 1880 and 1900?</t>
-  </si>
-  <si>
     <t>SELECT ?motif ?label (COUNT(DISTINCT ?work) AS ?nb) WHERE {   
   ?work a lrm:F1_Work ;         
         dcterms:issued ?date .         
@@ -1023,9 +997,6 @@
       </rPr>
       <t>?</t>
     </r>
-  </si>
-  <si>
-    <t>Which narrative events occur simultaneously in a given work?</t>
   </si>
   <si>
     <t>Which real geographical places are referenced in the corpus?</t>
@@ -1148,9 +1119,6 @@
     <t>Which characters share the same psychological state across different works?</t>
   </si>
   <si>
-    <t>Which narrative events involve a "novum"-type object and an antagonist character?</t>
-  </si>
-  <si>
     <t>SELECT DISTINCT ?event ?label WHERE {   
   ?event a gc:G5_Narrative_Event ;          
          crm:P16_used_specific_object ?novum ;          
@@ -1179,9 +1147,6 @@
 ORDER BY DESC(?nb)</t>
   </si>
   <si>
-    <t>Which biographical traits are most frequent among protagonists in the corpus?</t>
-  </si>
-  <si>
     <t>SELECT ?work ?label WHERE {   
   ?work a lrm:F1_Work ;         
         gc:GP0_has_feature sf:Feature_first_person_narrator .   
@@ -1268,9 +1233,6 @@
     <t>lrm:F1_Work ; gc:G0_Character-Stoff ; gc:G1_Character</t>
   </si>
   <si>
-    <t>lrm:F1_Work ; gc:G0_Character-Stoff ; gc:G1_Character ; crm:E55_Type</t>
-  </si>
-  <si>
     <t>lrm:F1_Work ; gc:G17_Character_Feature</t>
   </si>
   <si>
@@ -1433,12 +1395,6 @@
     <t>dlp:plays ; dlp:proper-part-of</t>
   </si>
   <si>
-    <t>dul:Organization ; crm:E55_Type</t>
-  </si>
-  <si>
-    <t>crm:P67i_is_referred_to_by ; crm:P2_has_type</t>
-  </si>
-  <si>
     <t>dul:Community ; gc:G1_Character</t>
   </si>
   <si>
@@ -1500,9 +1456,6 @@
   </si>
   <si>
     <t>gc:G4_Social_Relationship ; sf:H4_Non-human_Character</t>
-  </si>
-  <si>
-    <t>csm:geographical-place ; gc:G13_Narrative_Location</t>
   </si>
   <si>
     <t>gc:G13_Narrative_Location ; csm:geographical-place ; lrm:F1_Work</t>
@@ -1698,9 +1651,6 @@
 ORDER BY DESC(?nb)</t>
   </si>
   <si>
-    <t>Which narrative motifs are exclusively associated with Jules Verne's works in the corpus?</t>
-  </si>
-  <si>
     <t>SELECT DISTINCT ?motif ?label WHERE {
   ?motif a gc:G14_Narrative-Stoff .
   OPTIONAL { ?motif rdfs:label ?label . }
@@ -1863,9 +1813,6 @@
     <t>dul:Organization</t>
   </si>
   <si>
-    <t>Which types of academic organizations appear in the corpus?</t>
-  </si>
-  <si>
     <t>SELECT ?type ?label (COUNT(?org) AS ?nb) WHERE {
   ?org a dul:Organization ;
        crm:P2_has_type sf:type_academic_institution .
@@ -2120,12 +2067,6 @@
   </si>
   <si>
     <t>Which characters experience "love" psychological state?</t>
-  </si>
-  <si>
-    <t>gc:G3_Psychological_State, gc:G1_Characters</t>
-  </si>
-  <si>
-    <t>crm:P2_has_type, dlpfun:state-of</t>
   </si>
   <si>
     <t>SELECT ?char ?label WHERE {
@@ -2197,15 +2138,6 @@
 GROUP BY ?type ?work</t>
   </si>
   <si>
-    <t>gc:G3_Psychological_State, gc:G5_Narrative_Event</t>
-  </si>
-  <si>
-    <t>crm:P2_has_type, dlpfun:state-of, gc:GP1_is_character_in</t>
-  </si>
-  <si>
-    <t>Which psychological states are most frequently associated with antagonists across the corpus?</t>
-  </si>
-  <si>
     <t>SELECT ?type ?label (COUNT(?state) AS ?nb) WHERE {
   ?state a gc:G3_Psychological_State ;
          crm:P2_has_type ?type ;
@@ -2217,18 +2149,6 @@
 ORDER BY DESC(?nb)</t>
   </si>
   <si>
-    <t>crm:P2_has_type, dlpfun:state-of, dlp:plays</t>
-  </si>
-  <si>
-    <t>gc:G3_Psychological_State, gc:G1_Characters, crm:E55_Type</t>
-  </si>
-  <si>
-    <t>gc:G3_Psychological_State, gc:G5_Narrative_Event, gc:G1_Character, crm:E55_Type</t>
-  </si>
-  <si>
-    <t>gc:G3_Psychological_State, gc:G1_Character, crm:E55_Type, G10_Narrative_Function</t>
-  </si>
-  <si>
     <t>SELECT ?event ?eventLabel ?stateBefore ?stateAfter WHERE {
   ?stateBefore a gc:G3_Psychological_State ;
                dlptem:precedes ?event .
@@ -2243,9 +2163,6 @@
     <t>Which narrative events trigger a change of psychological state?</t>
   </si>
   <si>
-    <t>dlptem:precedes, dlptem:follows</t>
-  </si>
-  <si>
     <t>SELECT ?char ?label (COUNT(DISTINCT ?state) AS ?nb) WHERE {
   ?state a gc:G3_Psychological_State ;
          dlpfun:state-of ?char .
@@ -2256,12 +2173,6 @@
 ORDER BY DESC(?nb)</t>
   </si>
   <si>
-    <t>lrm:F1_Work, gc:G3_Psychological_State</t>
-  </si>
-  <si>
-    <t>dlpfun:state-of, gc:G1_is_character_in</t>
-  </si>
-  <si>
     <t>SELECT ?char ?role WHERE {
   ?assign a sf:H7_Relationship_Assignment ;
           sf:HP11_for_relationship sf:Rel_Marius_MariusFather ;
@@ -2295,12 +2206,6 @@
     </r>
   </si>
   <si>
-    <t>sf:HP11_for_relationship, sf:HP12i_is_relation_of, dlpext:d-uses</t>
-  </si>
-  <si>
-    <t>sf:H7_Relationship_Assignment, gc:G4_Social_Relationship, gc:G1_Character, gc:G6_Relationship_Role</t>
-  </si>
-  <si>
     <t>SELECT ?rel ?role ?relLabel WHERE {
   ?assign a sf:H7_Relationship_Assignment ;
           sf:HP12i_is_relation_of sf:Marius ;
@@ -2321,9 +2226,6 @@
           dolce:generic-dependant-on ?event .
   OPTIONAL { ?assign rdfs:label ?label . }
 }</t>
-  </si>
-  <si>
-    <t>sf:H7_Relationship_Assignment, gc:G5_Narrative_Event</t>
   </si>
   <si>
     <t>dolce:generic-dependant-on</t>
@@ -2354,9 +2256,6 @@
   </si>
   <si>
     <t>sf:HP12i_is_relation_of</t>
-  </si>
-  <si>
-    <t>sf:H7_Relationship_Assignment, gc:G1_Character</t>
   </si>
   <si>
     <t>Which relationships are grounded in the same event?</t>
@@ -2373,12 +2272,6 @@
 HAVING (COUNT(DISTINCT ?rel) &gt; 1)</t>
   </si>
   <si>
-    <t>sf:H7_Relationship_Assignment, gc:G5_Narrative_Event, gc:G4_Social_Relationship</t>
-  </si>
-  <si>
-    <t>sf:HP11_for_relationship, dolce:generic-dependant-on</t>
-  </si>
-  <si>
     <t>Which roles are most frequently assigned across all relationships in the corpus?</t>
   </si>
   <si>
@@ -2391,9 +2284,6 @@
 ORDER BY DESC(?nb)</t>
   </si>
   <si>
-    <t>sf:H7_Relationship_Assignment, gc:G6_Relationship_Role</t>
-  </si>
-  <si>
     <t>dlpext:d-uses</t>
   </si>
   <si>
@@ -2417,9 +2307,6 @@
         crm:P2_has_type sf:psychological_feature .
   OPTIONAL { ?feat rdfs:label ?label . }
 }</t>
-  </si>
-  <si>
-    <t>gc:G17_Character_Feature, crm:E55_Type</t>
   </si>
   <si>
     <t>SELECT ?facet ?valence WHERE {
@@ -2444,9 +2331,6 @@
 ORDER BY DESC(?nb)</t>
   </si>
   <si>
-    <t>gc:GP0_has_feature, crm:P2_has_type</t>
-  </si>
-  <si>
     <t>Which psychological features are exclusively associated with antagonists?</t>
   </si>
   <si>
@@ -2459,9 +2343,6 @@
           sf:HP7_has_facet ?facet ;
           sf:HP8_has_valence ?valence .
 }</t>
-  </si>
-  <si>
-    <t>sf:HP7_has_facet, sf:HP8_has_valence, sf:HP9i_is_personality_of</t>
   </si>
   <si>
     <t>Which characters have a positive valence on a given facet?</t>
@@ -2487,9 +2368,6 @@
 }
 GROUP BY ?facet ?label
 ORDER BY DESC(?nb)</t>
-  </si>
-  <si>
-    <t>sf:HP7_has_facet, sf:HP8_has_valence</t>
   </si>
   <si>
     <t>Which characters share the same facet with the same valence?</t>
@@ -2505,15 +2383,6 @@
 GROUP BY ?facet ?valence
 HAVING (COUNT(DISTINCT ?char) &gt; 1)
 ORDER BY ?facet</t>
-  </si>
-  <si>
-    <t>sf:H5_Personality_Assignment, sf:HP6_Valence, gc:G1_Character</t>
-  </si>
-  <si>
-    <t>sf:H5_Personality_Assignment, sf:HP6_Valence, gc:G1_Character, gc:G17_Character_Feature</t>
-  </si>
-  <si>
-    <t>sf:H5_Personality_Assignment, sf:HP6_Valence, gc:G17_Character_Feature</t>
   </si>
   <si>
     <t>Which characters have exclusively negative personality assignments?</t>
@@ -2532,9 +2401,6 @@
             sf:HP8_has_valence sf:Positive_Valence .
   }
 }</t>
-  </si>
-  <si>
-    <t>sf:HP8_has_valence, sf:HP9i_is_personality_of</t>
   </si>
   <si>
     <t>SELECT DISTINCT ?facet ?facetLabel ?valence WHERE {
@@ -2553,12 +2419,6 @@
   }
 }
 ORDER BY ?facet</t>
-  </si>
-  <si>
-    <t>sf:HP7_has_facet, sf:HP8_has_valence, sf:HP9i_is_personality_of, dlp:plays</t>
-  </si>
-  <si>
-    <t>sf:H5_Personality_Assignment, sf:HP6_Valence, gc:G17_Character_Feature, gc:G1_Character, gc:G11_Narrative_Role</t>
   </si>
   <si>
     <t>Which psychological features are shared between protagonists and antagonists?</t>
@@ -2625,28 +2485,6 @@
     <t>What is the psychological profile of Marius?</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Which characters are linked by a "friend of" relationship in the book </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ignis</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> by Chousy?</t>
-    </r>
-  </si>
-  <si>
     <t>Which characters share similar psychological profiles (at least half of their facet+valence pairs in common)?</t>
   </si>
   <si>
@@ -2790,28 +2628,7 @@
     <t>Which facets are particularly associated with Jules Verne?</t>
   </si>
   <si>
-    <t>sf:H5_Personality_Assignment, sf:HP6_Valence, gc:G17_Character_Feature, gc:G1_Character</t>
-  </si>
-  <si>
-    <t>sf:H5_Personality_Assignment, sf:HP6_Valence, gc:G17_Character_Feature, gc:G1_Character, lrm:F1_Work</t>
-  </si>
-  <si>
-    <t>sf:H5_Personality_Assignment, sf:HP6_Valence, gc:G17_Character_Feature, gc:G1_Character, G11_Narrative_Role</t>
-  </si>
-  <si>
-    <t>sf:HP7_has_facet, sf:HP8_has_valence, sf:HP9i_is_personality_of, dcterms:creator, gc:GP1_is_character_in</t>
-  </si>
-  <si>
-    <t>sf:HP7_has_facet, sf:HP8_has_valence, sf:HP9i_is_personality_of, dcterms:issued, gc:GP1_is_character_in</t>
-  </si>
-  <si>
-    <t>sf:HP7_has_facet, sf:HP8_has_valence, sf:HP9i_is_personality_of, gc:GP0_has_feature</t>
-  </si>
-  <si>
     <t>How many stories are there on the corpus?</t>
-  </si>
-  <si>
-    <t>How many authors are represented in the data?</t>
   </si>
   <si>
     <r>
@@ -2840,14 +2657,758 @@
     </r>
   </si>
   <si>
-    <t>How many stories are uploaded per year?</t>
+    <t>SELECT (COUNT(DISTINCT ?work) AS ?nb_works) WHERE {
+  ?work a lrm:F1_Work .
+}</t>
+  </si>
+  <si>
+    <t>SELECT (COUNT(DISTINCT ?author) AS ?nb_authors) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:creator ?author .
+}</t>
+  </si>
+  <si>
+    <t>SELECT ?author WHERE {
+  sf:LHomme_Bicycle_Work dcterms:creator ?author .
+}</t>
+  </si>
+  <si>
+    <t>SELECT ?year (COUNT(DISTINCT ?work) AS ?nb_works) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:issued ?year .
+}
+GROUP BY ?year
+ORDER BY ?year</t>
+  </si>
+  <si>
+    <t>How many stories are published per year?</t>
+  </si>
+  <si>
+    <t>Which narrative events occur simultaneously?</t>
+  </si>
+  <si>
+    <t>dlpcom:geographical-place ; gc:G13_Narrative_Location</t>
+  </si>
+  <si>
+    <t>ajouter un filtre pour être sûr que c'est un E55 fabula ou E55 syuzhet</t>
+  </si>
+  <si>
+    <t>Which narrative events involve a novum and an antagonist character?</t>
+  </si>
+  <si>
+    <t>SELECT ?org ?label WHERE {   
+  ?org a dul:Organization ;        
+         crm:P67i_is_referred_to_by sf:LHomme_Bicycle_Work ;        
+         rdfs:label ?label .   
+}</t>
+  </si>
+  <si>
+    <t>Which narrative events are temporally ordered (one preceding another)?</t>
+  </si>
+  <si>
+    <t>SELECT ?event1 ?label1 ?event2 ?label2 WHERE {
+  ?event1 a gc:G5_Narrative_Event ;
+          dlptem:precedes ?event2 .
+  ?event2 a gc:G5_Narrative_Event .
+  OPTIONAL { ?event1 rdfs:label ?label1 . }
+  OPTIONAL { ?event2 rdfs:label ?label2 . }
+}</t>
+  </si>
+  <si>
+    <t>Which time-intervals are associated with narrative events?</t>
+  </si>
+  <si>
+    <t>SELECT ?event ?eventLabel ?interval ?intervalLabel ?type WHERE {
+  ?interval a dlp:time-interval ;
+            dlptem:temporal-location-of ?event .
+  ?event a gc:G5_Narrative_Event .
+  OPTIONAL { ?event rdfs:label ?eventLabel . }
+  OPTIONAL { ?interval rdfs:label ?intervalLabel . }
+  OPTIONAL { ?interval crm:P2_has_type ?type . }
+}</t>
+  </si>
+  <si>
+    <t>dlptem:precedes</t>
+  </si>
+  <si>
+    <t>dlp:time-interval ; gc:G5_Narrative_Event</t>
+  </si>
+  <si>
+    <t>dlptem:temporal-location-of</t>
+  </si>
+  <si>
+    <t>Which narrative events occur within the same time-interval?</t>
+  </si>
+  <si>
+    <t>SELECT ?interval ?intervalLabel
+  (GROUP_CONCAT(?eventLabel; SEPARATOR=", ") AS ?events) WHERE {
+  ?interval a dlp:time-interval .
+  ?event1 a gc:G5_Narrative_Event ;
+          rdfs:label ?eventLabel .
+  ?interval dlptem:temporal-location-of ?event1 .
+  OPTIONAL { ?interval rdfs:label ?intervalLabel . }
+}
+GROUP BY ?interval ?intervalLabel
+HAVING (COUNT(DISTINCT ?event1) &gt; 1)</t>
+  </si>
+  <si>
+    <t>Which communities and organizations include non-human characters?</t>
+  </si>
+  <si>
+    <t>SELECT ?group ?groupLabel ?char ?charLabel WHERE {
+  { ?group a dul:Community . } UNION { ?group a dul:Organization . }
+  ?group dul:hasMember ?char .
+  ?char a sf:H4_Non-human_Character .
+  OPTIONAL { ?group rdfs:label ?groupLabel . }
+  OPTIONAL { ?char rdfs:label ?charLabel . }
+}</t>
+  </si>
+  <si>
+    <t>dul:Organization ; sf:H4_Non-human_Character</t>
+  </si>
+  <si>
+    <t>Which narrative locations appear in works published between 1880 and 1900?</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT ?loc ?locLabel (COUNT(DISTINCT ?work) AS ?nb) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:issued ?date .
+  FILTER(xsd:integer(str(?date)) &gt;= 1880 &amp;&amp; xsd:integer(str(?date)) &lt; 1900)
+  ?loc a gc:G13_Narrative_Location ;
+       crm:P67i_is_referred_to_by ?work .
+  OPTIONAL { ?loc rdfs:label ?locLabel . }
+}
+GROUP BY ?loc ?locLabel
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>Which narrative locations without real-world equivalents are associated with a future or indeterminate time-interval?</t>
+  </si>
+  <si>
+    <t>SELECT ?loc ?locLabel ?interval ?intervalLabel WHERE {
+  ?loc a gc:G13_Narrative_Location .
+  OPTIONAL { ?loc rdfs:label ?locLabel . }
+  FILTER NOT EXISTS { ?loc crm:P67_refers_to ?real . }
+  ?setting a gc:G12_Setting ;
+           crm:P67_refers_to ?loc .
+  ?interval a dlp:time-interval ;
+            dlpext:setting ?setting ;
+            crm:P2_has_type ?timeType .
+  FILTER(?timeType IN (sf:type_indeterminate_future, sf:type_future))
+  OPTIONAL { ?interval rdfs:label ?intervalLabel . }
+}</t>
+  </si>
+  <si>
+    <t>Which objects appear in more than one work, and are they novums?</t>
+  </si>
+  <si>
+    <t>SELECT ?obj ?label (COUNT(DISTINCT ?work) AS ?nb) ?isNovum WHERE {
+  ?obj a gc:G16_Object ;
+       crm:P67i_is_referred_to_by ?work .
+  OPTIONAL { ?obj rdfs:label ?label . }
+  BIND(EXISTS { ?obj a sf:H2_Concrete_Novum } AS ?isNovum)
+}
+GROUP BY ?obj ?label ?isNovum
+HAVING (COUNT(DISTINCT ?work) &gt; 1)
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>SELECT ?org ?label WHERE {
+  ?org a dul:Organization .
+  OPTIONAL { ?org rdfs:label ?label . }
+  FILTER EXISTS {
+    ?org dul:hasMember ?member .
+  }
+  FILTER NOT EXISTS {
+    ?org dul:hasMember ?member .
+    FILTER NOT EXISTS { ?member a sf:H3_Human_Character . }
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which organizations contain only human characters?</t>
+  </si>
+  <si>
+    <t>dcterms:issued ; crm:P67i_is_referred_to_by</t>
+  </si>
+  <si>
+    <t>gc:G13_Narrative_Location ; gc:G12_Setting ; dlp:time-interval</t>
+  </si>
+  <si>
+    <t>crm:P67_refers_to ; dlpext:setting ; crm:P2_has_type</t>
+  </si>
+  <si>
+    <t>gc:G16_Object ; lrm:F1_Work ; H2_Concrete_Novum</t>
+  </si>
+  <si>
+    <t>dul:Organization ; sf:H3_Human_Character</t>
+  </si>
+  <si>
+    <t>Which settings are associated with a time-interval?</t>
+  </si>
+  <si>
+    <t>gc:G12_Setting ; dlp:time-interval</t>
+  </si>
+  <si>
+    <t>dlpext:setting</t>
+  </si>
+  <si>
+    <t>SELECT ?setting ?settingLabel ?interval ?intervalLabel WHERE {
+  ?setting a gc:G12_Setting .
+  ?interval a dlp:time-interval ;
+            dlpext:setting ?setting .
+  OPTIONAL { ?setting rdfs:label ?settingLabel . }
+  OPTIONAL { ?interval rdfs:label ?intervalLabel . }
+}</t>
+  </si>
+  <si>
+    <t>Which groups are present in the corpus?</t>
+  </si>
+  <si>
+    <t>SELECT ?group ?label WHERE {
+  ?group a dul:Group .
+  OPTIONAL { ?group rdfs:label ?label . }
+}</t>
+  </si>
+  <si>
+    <t>Which characters belong to a group?</t>
+  </si>
+  <si>
+    <t>Which groups are referenced in more than one work?</t>
+  </si>
+  <si>
+    <t>SELECT ?group ?label (COUNT(DISTINCT ?work) AS ?nb) WHERE {
+  ?group a dul:Group ;
+         crm:P67i_is_referred_to_by ?work .
+  OPTIONAL { ?group rdfs:label ?label . }
+}
+GROUP BY ?group ?label
+HAVING (COUNT(DISTINCT ?work) &gt; 1)
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>dul:Group</t>
+  </si>
+  <si>
+    <t>SELECT ?char ?charLabel ?group ?groupLabel WHERE {
+  ?group a dul:Group ;
+         dul:hasMember ?char .
+  OPTIONAL { ?group rdfs:label ?groupLabel . }  OPTIONAL { ?char rdfs:label ?charLabel . }
+}</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; dul:Group</t>
+  </si>
+  <si>
+    <t>gc:G3_Psychological_State ; gc:G1_Characters ; crm:E55_Type</t>
+  </si>
+  <si>
+    <t>crm:P2_has_type ; dlpfun:state-of</t>
+  </si>
+  <si>
+    <t>gc:G3_Psychological_State ; gc:G1_Characters</t>
+  </si>
+  <si>
+    <t>gc:G3_Psychological_State; gc:G5_Narrative_Event</t>
+  </si>
+  <si>
+    <t>gc:G3_Psychological_State ; gc:G5_Narrative_Event</t>
+  </si>
+  <si>
+    <t>gc:G3_Psychological_State ; gc:G5_Narrative_Event ; gc:G1_Character ; crm:E55_Type</t>
+  </si>
+  <si>
+    <t>crm:P2_has_type ; dlpfun:state-of ; gc:GP1_is_character_in</t>
+  </si>
+  <si>
+    <t>gc:G3_Psychological_State ; gc:G1_Character ; crm:E55_Type ; G10_Narrative_Function</t>
+  </si>
+  <si>
+    <t>crm:P2_has_type ; dlpfun:state-of ; dlp:plays</t>
+  </si>
+  <si>
+    <t>dlptem:precedes ; dlptem:follows</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; gc:G3_Psychological_State</t>
+  </si>
+  <si>
+    <t>dlpfun:state-of ; gc:G1_is_character_in</t>
+  </si>
+  <si>
+    <t>sf:H7_Relationship_Assignment ; gc:G4_Social_Relationship ; gc:G1_Character ; gc:G6_Relationship_Role</t>
+  </si>
+  <si>
+    <t>sf:HP11_for_relationship ; sf:HP12i_is_relation_of ; dlpext:d-uses</t>
+  </si>
+  <si>
+    <t>sf:H7_Relationship_Assignment ; gc:G5_Narrative_Event</t>
+  </si>
+  <si>
+    <t>sf:H7_Relationship_Assignment ; gc:G1_Character</t>
+  </si>
+  <si>
+    <t>sf:H7_Relationship_Assignment ; gc:G5_Narrative_Event ; gc:G4_Social_Relationship</t>
+  </si>
+  <si>
+    <t>sf:HP11_for_relationship ; dolce:generic-dependant-on</t>
+  </si>
+  <si>
+    <t>sf:H7_Relationship_Assignment ; gc:G6_Relationship_Role</t>
+  </si>
+  <si>
+    <t>gc:G17_Character_Feature ; crm:E55_Type</t>
+  </si>
+  <si>
+    <t>sf:H5_Personality_Assignment ; sf:H6_Valence ; gc:G1_Character ; gc:G17_Character_Feature</t>
+  </si>
+  <si>
+    <t>sf:HP7_has_facet ; sf:HP8_has_valence ; sf:HP9i_is_personality_of</t>
+  </si>
+  <si>
+    <t>sf:H5_Personality_Assignment ; sf:H6_Valence ; gc:G17_Character_Feature ; gc:G1_Character ; gc:G11_Narrative_Role</t>
+  </si>
+  <si>
+    <t>sf:HP7_has_facet ; sf:HP8_has_valence ; sf:HP9i_is_personality_of ; dlp:plays</t>
+  </si>
+  <si>
+    <t>sf:H5_Personality_Assignment ; sf:H6_Valence ; gc:G17_Character_Feature</t>
+  </si>
+  <si>
+    <t>sf:HP7_has_facet ; sf:HP8_has_valence</t>
+  </si>
+  <si>
+    <t>sf:H5_Personality_Assignment ; sf:H6_Valence ; gc:G1_Character</t>
+  </si>
+  <si>
+    <t>sf:HP8_has_valence ; sf:HP9i_is_personality_of</t>
+  </si>
+  <si>
+    <t>sf:H5_Personality_Assignment ; sf:H6_Valence ; gc:G17_Character_Feature ; gc:G1_Character</t>
+  </si>
+  <si>
+    <t>sf:H5_Personality_Assignment ; sf:H6_Valence ; gc:G17_Character_Feature ; gc:G1_Character ; lrm:F1_Work</t>
+  </si>
+  <si>
+    <t>sf:HP7_has_facet ; sf:HP8_has_valence ; sf:HP9i_is_personality_of ; dcterms:creator ; gc:GP1_is_character_in</t>
+  </si>
+  <si>
+    <t>sf:HP7_has_facet ; sf:HP8_has_valence ; sf:HP9i_is_personality_of ; dcterms:issued ; gc:GP1_is_character_in</t>
+  </si>
+  <si>
+    <t>sf:H5_Personality_Assignment ; sf:H6_Valence ; gc:G17_Character_Feature ; gc:G1_Character ; G11_Narrative_Role</t>
+  </si>
+  <si>
+    <t>sf:HP7_has_facet ; sf:HP8_has_valence ; sf:HP9i_is_personality_of ; gc:GP0_has_feature</t>
+  </si>
+  <si>
+    <t>Which works share the same combination of textual features?</t>
+  </si>
+  <si>
+    <t>SELECT ?work1 ?label1 ?work2 ?label2
+  (COUNT(DISTINCT ?feature) AS ?shared) WHERE {
+  ?work1 gc:GP0_has_feature ?feature .
+  ?work2 gc:GP0_has_feature ?feature .
+  ?feature a gc:G18_Textual_Feature .
+  FILTER(?work1 != ?work2 &amp;&amp; STR(?work1) &lt; STR(?work2))
+  OPTIONAL { ?work1 rdfs:label ?label1 . }
+  OPTIONAL { ?work2 rdfs:label ?label2 . }
+}
+GROUP BY ?work1 ?label1 ?work2 ?label2
+ORDER BY DESC(?shared)</t>
+  </si>
+  <si>
+    <t>Which works use a heterodiegetic narrator?</t>
+  </si>
+  <si>
+    <t>SELECT ?work ?label WHERE {
+  ?work gc:GP0_has_feature sf:Feature_heterodiegetic_narrator .
+  OPTIONAL { ?work rdfs:label ?label . }
+}</t>
+  </si>
+  <si>
+    <t>Which textual features are exclusively associated with works published before 1900?</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT ?feature ?label WHERE {
+  ?feature a gc:G18_Textual_Feature .
+  OPTIONAL { ?feature rdfs:label ?label . }
+  FILTER EXISTS {
+    ?work gc:GP0_has_feature ?feature ;
+          dcterms:issued ?date .
+    FILTER(xsd:integer(str(?date)) &lt; 1900)
+  }
+  FILTER NOT EXISTS {
+    ?work2 gc:GP0_has_feature ?feature ;
+           dcterms:issued ?date2 .
+    FILTER(xsd:integer(str(?date2)) &gt;= 1900)
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which narrator types are most frequent in the corpus?</t>
+  </si>
+  <si>
+    <t>SELECT ?feature ?label (COUNT(DISTINCT ?work) AS ?nb) WHERE {
+  ?work gc:GP0_has_feature ?feature .
+  ?feature a gc:G18_Textual_Feature ;
+           crm:P2_has_type sf:type_narrator .
+  OPTIONAL { ?feature rdfs:label ?label . }
+}
+GROUP BY ?feature ?label
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>Which authors tend to use the same textual features across their works?</t>
+  </si>
+  <si>
+    <t>SELECT ?author ?feature ?featureLabel (COUNT(DISTINCT ?work) AS ?nb) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:creator ?author ;
+        gc:GP0_has_feature ?feature .
+  ?feature a gc:G18_Textual_Feature .
+  OPTIONAL { ?feature rdfs:label ?featureLabel . }
+}
+GROUP BY ?author ?feature ?featureLabel
+HAVING (COUNT(DISTINCT ?work) &gt; 1)
+ORDER BY ?author DESC(?nb)</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; gc:G18_Textual_Feature</t>
+  </si>
+  <si>
+    <t>dcterms:creator ; gc:GP0_has_feature</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Which narrative motifs appear in more than [number] works in the corpus?</t>
+  </si>
+  <si>
+    <t>Which character archetypes appear in more than [number] works in the corpus?</t>
+  </si>
+  <si>
+    <t>Which characters appear in more than [number] works in the corpus?</t>
+  </si>
+  <si>
+    <t>Which character archetypes appear most frequently in a dystopia register?</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; gc:G0_Character-Stoff ; gc:G1_Character ; crm:E55_Type ; G18_Textual_Feature</t>
+  </si>
+  <si>
+    <t>Which character archetypes appear most frequently in a [register in G18_Textual_Feature] register?</t>
+  </si>
+  <si>
+    <t>Which works use [narrator in G18_Textual_Feature] narration?</t>
+  </si>
+  <si>
+    <t>Which characters play a [G11_Narrative_Role]?</t>
+  </si>
+  <si>
+    <t>Which characters play a hero role?</t>
+  </si>
+  <si>
+    <t>Which characters are human?</t>
+  </si>
+  <si>
+    <t>sf:H3_Human_Character</t>
+  </si>
+  <si>
+    <t>SELECT ?char WHERE { 
+  ?char a sf:H3_Human_Character . 
+}</t>
+  </si>
+  <si>
+    <t>Which works are a [register in G18_Textual_Feature]?</t>
+  </si>
+  <si>
+    <t>Which works were published before 1900?</t>
+  </si>
+  <si>
+    <t>Which works were published before [date]?</t>
+  </si>
+  <si>
+    <t>Which works were published after 1900?</t>
+  </si>
+  <si>
+    <t>Which works were published after [date]?</t>
+  </si>
+  <si>
+    <t>SELECT ?work ?label ?date WHERE {
+  ?work a lrm:F1_Work ;
+        rdfs:label ?label ;
+        dcterms:issued ?date .
+  FILTER (xsd:integer(str(?date)) &gt; 1900)
+}
+ORDER BY ?date</t>
+  </si>
+  <si>
+    <t>What are [G1_Character]'s defining features?</t>
+  </si>
+  <si>
+    <t>Who are the characters in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Who are the human characters in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>What is the spatio-temporal setting of [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Which characters are connected in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Which novum are featured in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>What narrative events make up [F1_Work]?</t>
+  </si>
+  <si>
+    <t>In what chronological order do the events in [F1_Work] unfold?</t>
+  </si>
+  <si>
+    <t>Which events involve [G1_Character] in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>What physical characteristics are described in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>What narrative roles are embodied in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Which organizations are mentioned in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>What is the earliest expression of [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Which narrative units feature [G1_Character] as the subject in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Which narrative units serve a [G10_Narrative_Function] in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Which characters share the same traits in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Which character serves as the [G10_Narrative_Function] in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>How many distinct narrative roles are defined in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>How many narrative units are there per participant in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Which communities does [G1_Character] belong to?</t>
+  </si>
+  <si>
+    <t>Who are the members of the [Organization/Community]?</t>
+  </si>
+  <si>
+    <t>passer ça en feature</t>
+  </si>
+  <si>
+    <t>Which features are shared by more than [number] works?</t>
+  </si>
+  <si>
+    <t>Which features are shared by more than three works?</t>
+  </si>
+  <si>
+    <t>Which works instantiate the [G14_Narrative-Stoff] archetype?</t>
+  </si>
+  <si>
+    <t>Which archetypes are exclusively associated with [G11_Narrative_Role]?</t>
+  </si>
+  <si>
+    <t>Which patterns are exclusively associated with dystopia subgenre?</t>
+  </si>
+  <si>
+    <t>Which patterns are exclusively associated with [subgenre in G18_Textual_Feature]</t>
+  </si>
+  <si>
+    <t>Which narrative patterns are most frequent between [date] and [date]?</t>
+  </si>
+  <si>
+    <t>Which narrative patterns are most frequent between 1880 and 1900?</t>
+  </si>
+  <si>
+    <t>Which characters are linked by a [G6_Relationship_Role] in [F1_Work]?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Which characters are linked by a "friend of" relationship in </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ignis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by Chousy?</t>
+    </r>
+  </si>
+  <si>
+    <t>How does the syuzhet of [F1_Work] differ from its fabula?</t>
+  </si>
+  <si>
+    <t>Which narrative units compose the narrative sequence of [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Which works share the same sequence of [number] narrative functions?</t>
+  </si>
+  <si>
+    <t>Which characters play the [G11_Narrative_Role] in the corpus?</t>
+  </si>
+  <si>
+    <t>Which psychological states are most frequently associated with [G11_Narrative_Role]?</t>
+  </si>
+  <si>
+    <t>Which narrative events involve a novum and a [G11_Narrative_Role] character?</t>
+  </si>
+  <si>
+    <t>Which biographical traits are most frequent among [G11_Narrative_Role]?</t>
+  </si>
+  <si>
+    <t>Which biographical traits are most frequent among protagonists?</t>
+  </si>
+  <si>
+    <t>Which works in the corpus use [narrator]?</t>
+  </si>
+  <si>
+    <t>Which novums appear in more than [number] works by [author]?</t>
+  </si>
+  <si>
+    <t>Which types of non-human characters does [author] portray?</t>
+  </si>
+  <si>
+    <t>Which narrative locations does [author] situate outside [location]</t>
+  </si>
+  <si>
+    <t>Which stories were inspired by [location]?</t>
+  </si>
+  <si>
+    <t>Which character archetypes does [author] use most frequently?</t>
+  </si>
+  <si>
+    <t>Which Proppian functions are systematically present across [author]'s works?</t>
+  </si>
+  <si>
+    <t>Which types of settings does [author] use most frequently?</t>
+  </si>
+  <si>
+    <t>Which narrative patterns are exclusively associated with Jules Verne's works?</t>
+  </si>
+  <si>
+    <t>Which narrative patterns are exclusively associated with [author]'s works?</t>
+  </si>
+  <si>
+    <t>Which types of novums does [author] associate with scientist characters?</t>
+  </si>
+  <si>
+    <t>What is the distribution of Proppian roles across [author]'s works?</t>
+  </si>
+  <si>
+    <t>Which psychological states are most frequent among [author]'s [G11_Narrative_Role]?</t>
+  </si>
+  <si>
+    <t>Which types of [type of Organization] appear in the corpus</t>
+  </si>
+  <si>
+    <t>Which academic organizations appear in the corpus?</t>
+  </si>
+  <si>
+    <t>Which character archetypes evolved from [G11_Narrative_Role] to [G11_Narrative_Role] across different works?</t>
+  </si>
+  <si>
+    <t>Which characters evolve from [G11_Narrative_Role] to [G11_Narrative_Role] in the same work?</t>
+  </si>
+  <si>
+    <t>Which characters experience [G3_Psychological_State] psychological state?</t>
+  </si>
+  <si>
+    <t>Which psychological state does [G1_Character] experience?</t>
+  </si>
+  <si>
+    <t>How many distinct psychological states does each character experience in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Which role does each character play in the relationship between [G1_Character] and [G1_Character]?</t>
+  </si>
+  <si>
+    <t>Which relationships is [G1_Character] involved in, and in what role?</t>
+  </si>
+  <si>
+    <t>Which characters play the [G6_Relationship_Role] in the corpus and in which relationships?</t>
+  </si>
+  <si>
+    <t>For the relationship between [G1_Character] and [G1_Character], who plays which role?</t>
+  </si>
+  <si>
+    <t>Which psychological features are exclusively associated with [G11_Narrative_Role]?</t>
+  </si>
+  <si>
+    <t>Which personality assignments are defined for [G1_Character]?</t>
+  </si>
+  <si>
+    <t>What is the psychological profile of [G1_Character]?</t>
+  </si>
+  <si>
+    <t>Which psychological features are shared between [G11_Narrative_Role] and [G11_Narrative_Role]?</t>
+  </si>
+  <si>
+    <t>Which personalities distinguish [G11_Narrative_Role] from [G11_Narrative_Role] (present in one group but not the other)?</t>
+  </si>
+  <si>
+    <t>Which characters have both [H6_Valence+psychological feature in G17_Character_Feature] and [H6_Valence+psychological feature in G17_Character_Feature]?</t>
+  </si>
+  <si>
+    <t>Which facets are particularly associated with [author]?</t>
+  </si>
+  <si>
+    <t>Which facets and valences are most represented between [date] and [date]?</t>
+  </si>
+  <si>
+    <t>What is the distribution of facets and valences among [G11_Narrative_Role]?</t>
+  </si>
+  <si>
+    <t>What is the distribution of facets and valences among [biographical feature in G17_Character_Feature]?</t>
+  </si>
+  <si>
+    <t>How many authors are represented in the corpus?</t>
+  </si>
+  <si>
+    <t>Who wrote [F1_Work]?</t>
+  </si>
+  <si>
+    <t>Which narrative locations appear in works published between [date] and [date]?</t>
+  </si>
+  <si>
+    <t>Which objects appear in more than [numer] work, and are they novums?</t>
+  </si>
+  <si>
+    <t>Which groups are referenced in more than [number] work?</t>
+  </si>
+  <si>
+    <t>Which textual features are exclusively associated with works published [before/after date]?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2894,6 +3455,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2909,7 +3477,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF5DD"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2952,7 +3520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2963,17 +3531,30 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3265,1918 +3846,2545 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="43.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="52.44140625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="43.77734375" style="12" customWidth="1"/>
+    <col min="2" max="4" width="43.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="3" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="E4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10"/>
+      <c r="B7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="10"/>
+      <c r="B8" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="s">
+        <v>507</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="E11" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10"/>
+      <c r="B13" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="E13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="6" t="s">
+    </row>
+    <row r="14" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="E14" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="10"/>
+      <c r="B16" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10"/>
+      <c r="B17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>519</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="6" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="E25" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D26" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="E26" s="7" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="E35" s="7" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="10"/>
+      <c r="B38" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="10"/>
+      <c r="B39" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="10"/>
+      <c r="B41" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="10"/>
+      <c r="B42" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A44" s="10"/>
+      <c r="B44" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="132" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="10"/>
+      <c r="B47" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="14"/>
+      <c r="B48" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="10"/>
+      <c r="B50" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="A52" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="170.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="10"/>
+      <c r="B56" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="10" t="s">
+        <v>550</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="A59" s="10"/>
+      <c r="B59" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A60" s="10"/>
+      <c r="B60" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="303.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A62" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="10"/>
+      <c r="B63" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="E63" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="10"/>
+      <c r="B64" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="F64" s="2"/>
+    </row>
+    <row r="65" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="10"/>
+      <c r="B65" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="A66" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A67" s="10"/>
+      <c r="B67" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F67" s="2"/>
+    </row>
+    <row r="68" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="10"/>
+      <c r="B68" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+      <c r="A69" s="10"/>
+      <c r="B69" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="10"/>
+      <c r="B70" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+      <c r="A71" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A72" s="10"/>
+      <c r="B72" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+      <c r="A73" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="10"/>
+      <c r="B74" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="10"/>
+      <c r="B75" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+      <c r="A78" s="10"/>
+      <c r="B78" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A79" s="14"/>
+      <c r="B79" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A80" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A81" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+      <c r="A82" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A83" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="224.4" x14ac:dyDescent="0.3">
+      <c r="A84" s="10" t="s">
+        <v>564</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A85" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="A86" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="132" x14ac:dyDescent="0.3">
+      <c r="A87" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="E87" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A88" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="A89" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A90" s="10"/>
+      <c r="B90" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="A91" s="10"/>
+      <c r="B91" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A92" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A93" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A94" s="10" t="s">
+        <v>574</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="10"/>
+      <c r="B95" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A96" s="10"/>
+      <c r="B96" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A97" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+      <c r="A98" s="10" t="s">
+        <v>576</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A99" s="10"/>
+      <c r="B99" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E99" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A100" s="10"/>
+      <c r="B100" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A101" s="10"/>
+      <c r="B101" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="E101" s="7" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A102" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E102" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="132" x14ac:dyDescent="0.3">
+      <c r="A103" s="10"/>
+      <c r="B103" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A104" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A105" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A106" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="E106" s="7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+      <c r="A107" s="10"/>
+      <c r="B107" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="E107" s="7" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A108" s="10" t="s">
+        <v>580</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="E108" s="7" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A109" s="10"/>
+      <c r="B109" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E109" s="7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="132" x14ac:dyDescent="0.3">
+      <c r="A110" s="10"/>
+      <c r="B110" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A111" s="10"/>
+      <c r="B111" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A112" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+      <c r="A113" s="10"/>
+      <c r="B113" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A114" s="10"/>
+      <c r="B114" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A115" s="10"/>
+      <c r="B115" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="211.2" x14ac:dyDescent="0.3">
+      <c r="A116" s="10" t="s">
+        <v>582</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="E116" s="7" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A117" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A119" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E119" s="7" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A120" s="10"/>
+      <c r="B120" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="A121" s="10"/>
+      <c r="B121" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="211.2" x14ac:dyDescent="0.3">
+      <c r="A122" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="E122" s="7" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A123" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="224.4" x14ac:dyDescent="0.3">
+      <c r="A124" s="10"/>
+      <c r="B124" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E124" s="7" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="224.4" x14ac:dyDescent="0.3">
+      <c r="A125" s="10"/>
+      <c r="B125" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A126" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="A127" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="198" x14ac:dyDescent="0.3">
+      <c r="A128" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E128" s="7" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" ht="198" x14ac:dyDescent="0.3">
+      <c r="A129" s="10"/>
+      <c r="B129" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E129" s="7" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A130" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="E130" s="7" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A131" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="E131" s="7" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A132" s="10"/>
+      <c r="B132" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" ht="66" x14ac:dyDescent="0.3">
+      <c r="A133" s="10"/>
+      <c r="B133" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A134" s="10" t="s">
+        <v>593</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A135" s="10"/>
+      <c r="B135" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A136" s="10"/>
+      <c r="B136" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A137" s="10"/>
+      <c r="B137" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A138" s="10"/>
+      <c r="B138" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A139" s="10"/>
+      <c r="B139" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A140" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="A141" s="10"/>
+      <c r="B141" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A142" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A143" s="10"/>
+      <c r="B143" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="105.6" x14ac:dyDescent="0.3">
+      <c r="A144" s="10"/>
+      <c r="B144" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A145" s="10"/>
+      <c r="B145" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A146" s="10"/>
+      <c r="B146" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A147" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A148" s="10"/>
+      <c r="B148" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" s="6" customFormat="1" ht="66" x14ac:dyDescent="0.3">
+      <c r="A149" s="15"/>
+      <c r="B149" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2"/>
+    </row>
+    <row r="150" spans="1:7" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="A150" s="10" t="s">
+        <v>597</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="A151" s="10"/>
+      <c r="B151" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="A152" s="10"/>
+      <c r="B152" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="10"/>
+      <c r="B153" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="D153" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="E153" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+    </row>
+    <row r="154" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="A154" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D154" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="9" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="9"/>
-    </row>
-    <row r="29" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="E29" s="2"/>
-      <c r="G29" s="9"/>
-    </row>
-    <row r="30" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="G30" s="9"/>
-    </row>
-    <row r="31" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="G33" s="9"/>
-    </row>
-    <row r="34" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="132" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="132" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="171.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="184.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="170.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="66" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="303.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="E64" s="2"/>
-    </row>
-    <row r="65" spans="1:5" ht="102" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="66" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E67" s="2"/>
-    </row>
-    <row r="68" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="132" x14ac:dyDescent="0.3">
-      <c r="A69" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="132" x14ac:dyDescent="0.3">
-      <c r="A71" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="132" x14ac:dyDescent="0.3">
-      <c r="A73" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="132" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A79" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A80" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A81" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="132" x14ac:dyDescent="0.3">
-      <c r="A82" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A83" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" ht="224.4" x14ac:dyDescent="0.3">
-      <c r="A84" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A85" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="171.6" x14ac:dyDescent="0.3">
-      <c r="A86" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="132" x14ac:dyDescent="0.3">
-      <c r="A87" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A88" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="171.6" x14ac:dyDescent="0.3">
-      <c r="A89" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A90" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="66" x14ac:dyDescent="0.3">
-      <c r="A91" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A93" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="184.8" x14ac:dyDescent="0.3">
-      <c r="A95" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="52.8" x14ac:dyDescent="0.3">
-      <c r="A96" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A97" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A98" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A99" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A100" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="B100" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="184.8" x14ac:dyDescent="0.3">
-      <c r="A101" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A102" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="132" x14ac:dyDescent="0.3">
-      <c r="A103" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" ht="118.8" x14ac:dyDescent="0.3">
-      <c r="A104" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A105" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A106" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A107" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A108" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A109" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="132" x14ac:dyDescent="0.3">
-      <c r="A110" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A111" s="6" t="s">
-        <v>395</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A112" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="D112" s="6" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="66" x14ac:dyDescent="0.3">
-      <c r="A113" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D113" s="6" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A114" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A115" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>407</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" ht="211.2" x14ac:dyDescent="0.3">
-      <c r="A116" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="79.2" x14ac:dyDescent="0.3">
-      <c r="A117" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A118" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="92.4" x14ac:dyDescent="0.3">
-      <c r="A119" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" ht="105.6" x14ac:dyDescent="0.3">
-      <c r="A120" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" ht="171.6" x14ac:dyDescent="0.3">
-      <c r="A121" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" ht="211.2" x14ac:dyDescent="0.3">
-      <c r="A122" s="6" t="s">
-        <v>428</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A123" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" ht="224.4" x14ac:dyDescent="0.3">
-      <c r="A124" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" ht="224.4" x14ac:dyDescent="0.3">
-      <c r="A125" s="6" t="s">
-        <v>436</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A126" s="6" t="s">
-        <v>438</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" ht="171.6" x14ac:dyDescent="0.3">
-      <c r="A127" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="B127" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>453</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" ht="198" x14ac:dyDescent="0.3">
-      <c r="A128" s="6" t="s">
-        <v>448</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" ht="198" x14ac:dyDescent="0.3">
-      <c r="A129" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="B129" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A130" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A131" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="1" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="1" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="1" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="1" t="s">
-        <v>459</v>
+      <c r="E154" s="7" t="s">
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/src/CQs.xlsx
+++ b/src/CQs.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F80401-FE6E-421C-92F6-591A78B7C330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A673ED-72EA-4A53-BB6D-7B7DEBACEE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11724" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CQs" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CQs!$C$1:$C$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CQs!$C$1:$C$137</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="519">
   <si>
     <t>CQ</t>
   </si>
@@ -720,9 +720,6 @@
   </si>
   <si>
     <t>lrm:F1_Work ; gc:G0_Character-Stoff</t>
-  </si>
-  <si>
-    <t>lrm:F1_Work ; gc:G12_Setting</t>
   </si>
   <si>
     <t>dul:Organization</t>
@@ -1165,9 +1162,6 @@
   </si>
   <si>
     <t>Which organizations are mentioned in [F1_Work]?</t>
-  </si>
-  <si>
-    <t>Which narrative units feature [G1_Character] as the subject in [F1_Work]?</t>
   </si>
   <si>
     <t>Which narrative units serve a [G10_Narrative_Function] in [F1_Work]?</t>
@@ -3000,16 +2994,6 @@
     <t>gc:G13_Narrative_Location ; lrm:F1_Work ; gc:G7_Narrative_Sequence ; gc:G5_Narrative_Event ; dlpcom:geographical-place</t>
   </si>
   <si>
-    <t>SELECT ?facet (COUNT(DISTINCT ?char) AS ?frequency) WHERE {
-  ?assignment a sf:H5_Personality_Assignment ;
-              sf:HP9i_is_personality_of ?char ;
-              sf:HP7_has_facet ?facet .
-  ?char a sf:H4_Non-Human_Character .
-}
-GROUP BY ?facet
-ORDER BY DESC(?frequency)</t>
-  </si>
-  <si>
     <t>What are all the relationships that involve both Hermann Bakermann and Cesar Puck?</t>
   </si>
   <si>
@@ -3029,12 +3013,42 @@
   <si>
     <t>What are all the relationships that involve both [G1_Character] and [G1_Character]?</t>
   </si>
+  <si>
+    <t>In which narrative events is [G1_Character] involved in [F1_Work]?</t>
+  </si>
+  <si>
+    <t>SELECT ?facet (COUNT(DISTINCT ?char) AS ?frequency) WHERE {
+  ?assignment a sf:H5_Personality_Assignment ;
+              sf:HP9i_is_personality_of ?char ;
+              sf:HP7_has_facet ?facet .
+  ?char a sf:H4_Non-human_Character .
+}
+GROUP BY ?facet
+ORDER BY DESC(?frequency)</t>
+  </si>
+  <si>
+    <t>Which objects are not novums?</t>
+  </si>
+  <si>
+    <t>SELECT ?obj WHERE {
+  ?obj a gc:G16_Object .
+  FILTER NOT EXISTS {
+    ?obj a sf:H2_Concrete_Novum
+  }
+}</t>
+  </si>
+  <si>
+    <t>gc:G16_Object ; sf:H2_Concrete_Novum</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; gc:G12_Setting ; crm:E55_Type</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3068,25 +3082,12 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3140,7 +3141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3154,9 +3155,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3166,10 +3164,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
@@ -3462,19 +3457,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G136"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="43.77734375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="43.77734375" style="10" customWidth="1"/>
     <col min="2" max="4" width="43.77734375" style="1" customWidth="1"/>
     <col min="5" max="5" width="52.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="13" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="11" customWidth="1"/>
     <col min="7" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -3488,11 +3483,11 @@
       <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="13"/>
+      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>222</v>
+      <c r="A2" s="8" t="s">
+        <v>221</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
@@ -3509,26 +3504,26 @@
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>310</v>
-      </c>
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>221</v>
+      <c r="A4" s="8" t="s">
+        <v>220</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>5</v>
@@ -3537,39 +3532,39 @@
         <v>63</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
         <v>224</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>225</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>59</v>
@@ -3579,7 +3574,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="6" t="s">
         <v>6</v>
       </c>
@@ -3590,11 +3585,11 @@
         <v>61</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="6" t="s">
         <v>35</v>
       </c>
@@ -3602,31 +3597,31 @@
         <v>75</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
+      <c r="A10" s="8"/>
       <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
@@ -3639,8 +3634,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>231</v>
+      <c r="A11" s="8" t="s">
+        <v>230</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>11</v>
@@ -3652,27 +3647,27 @@
         <v>59</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
+      <c r="A12" s="8"/>
       <c r="B12" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>109</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9"/>
+      <c r="A13" s="8"/>
       <c r="B13" s="6" t="s">
         <v>3</v>
       </c>
@@ -3683,13 +3678,13 @@
         <v>67</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
+      <c r="A14" s="8"/>
       <c r="B14" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>78</v>
@@ -3698,28 +3693,28 @@
         <v>68</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>233</v>
+      <c r="A15" s="8" t="s">
+        <v>232</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9"/>
+      <c r="A16" s="8"/>
       <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
@@ -3730,12 +3725,12 @@
         <v>69</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>237</v>
+      <c r="A17" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>12</v>
@@ -3747,12 +3742,12 @@
         <v>58</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>238</v>
+      <c r="A18" s="8" t="s">
+        <v>237</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>16</v>
@@ -3764,46 +3759,46 @@
         <v>58</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
-        <v>236</v>
+      <c r="A19" s="8" t="s">
+        <v>235</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>80</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="9" t="s">
-        <v>240</v>
+      <c r="A20" s="8" t="s">
+        <v>239</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
-        <v>241</v>
+      <c r="A21" s="8" t="s">
+        <v>240</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>17</v>
@@ -3815,12 +3810,12 @@
         <v>70</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="5" customFormat="1" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
-        <v>242</v>
+      <c r="A22" s="9" t="s">
+        <v>241</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>27</v>
@@ -3829,16 +3824,16 @@
         <v>84</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="F22" s="14"/>
+        <v>321</v>
+      </c>
+      <c r="F22" s="12"/>
     </row>
     <row r="23" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
-        <v>243</v>
+      <c r="A23" s="8" t="s">
+        <v>242</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>19</v>
@@ -3850,12 +3845,12 @@
         <v>85</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
-        <v>244</v>
+      <c r="A24" s="8" t="s">
+        <v>243</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>20</v>
@@ -3864,15 +3859,15 @@
         <v>87</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
-        <v>239</v>
+      <c r="A25" s="8" t="s">
+        <v>238</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>21</v>
@@ -3881,18 +3876,18 @@
         <v>88</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
-        <v>249</v>
+      <c r="A26" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>82</v>
@@ -3901,13 +3896,13 @@
         <v>89</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
-        <v>245</v>
+      <c r="A27" s="8" t="s">
+        <v>244</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>23</v>
@@ -3916,16 +3911,16 @@
         <v>76</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
-        <v>250</v>
+      <c r="A28" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>24</v>
@@ -3934,16 +3929,16 @@
         <v>90</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
-        <v>251</v>
+      <c r="A29" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>25</v>
@@ -3952,33 +3947,33 @@
         <v>76</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="12" t="s">
-        <v>247</v>
+      <c r="A30" s="8" t="s">
+        <v>513</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>87</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="9" t="s">
-        <v>248</v>
+      <c r="A31" s="8" t="s">
+        <v>246</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>34</v>
@@ -3987,83 +3982,83 @@
         <v>92</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="9" t="s">
-        <v>252</v>
+      <c r="A32" s="8" t="s">
+        <v>250</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>91</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="9" t="s">
-        <v>246</v>
+      <c r="A33" s="8" t="s">
+        <v>245</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>70</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
-        <v>253</v>
+      <c r="A34" s="8" t="s">
+        <v>251</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>93</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E34" s="6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>338</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>340</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>93</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
+      <c r="A36" s="8"/>
       <c r="B36" s="6" t="s">
         <v>28</v>
       </c>
@@ -4074,11 +4069,11 @@
         <v>71</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
+      <c r="A37" s="8"/>
       <c r="B37" s="6" t="s">
         <v>29</v>
       </c>
@@ -4087,11 +4082,11 @@
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
+      <c r="A38" s="8"/>
       <c r="B38" s="6" t="s">
         <v>30</v>
       </c>
@@ -4099,14 +4094,14 @@
         <v>78</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
+      <c r="A39" s="8"/>
       <c r="B39" s="6" t="s">
         <v>31</v>
       </c>
@@ -4121,7 +4116,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
+      <c r="A40" s="8"/>
       <c r="B40" s="6" t="s">
         <v>32</v>
       </c>
@@ -4132,11 +4127,11 @@
         <v>73</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
+      <c r="A41" s="8"/>
       <c r="B41" s="6" t="s">
         <v>33</v>
       </c>
@@ -4145,11 +4140,11 @@
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
+      <c r="A42" s="8"/>
       <c r="B42" s="6" t="s">
         <v>36</v>
       </c>
@@ -4157,15 +4152,15 @@
         <v>97</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>470</v>
-      </c>
-      <c r="F42" s="15"/>
+        <v>468</v>
+      </c>
+      <c r="F42" s="13"/>
     </row>
     <row r="43" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="9"/>
+      <c r="A43" s="8"/>
       <c r="B43" s="6" t="s">
         <v>37</v>
       </c>
@@ -4176,28 +4171,28 @@
         <v>70</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="9" t="s">
-        <v>255</v>
+      <c r="A44" s="8" t="s">
+        <v>253</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="9"/>
+      <c r="A45" s="8"/>
       <c r="B45" s="6" t="s">
         <v>41</v>
       </c>
@@ -4212,11 +4207,11 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="9" t="s">
-        <v>304</v>
+      <c r="A46" s="8" t="s">
+        <v>302</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>99</v>
@@ -4225,11 +4220,11 @@
         <v>100</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
+      <c r="A47" s="8"/>
       <c r="B47" s="6" t="s">
         <v>39</v>
       </c>
@@ -4244,8 +4239,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="9" t="s">
-        <v>257</v>
+      <c r="A48" s="8" t="s">
+        <v>255</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>42</v>
@@ -4257,95 +4252,95 @@
         <v>102</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="9" t="s">
-        <v>258</v>
+      <c r="A49" s="8" t="s">
+        <v>256</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D49" s="8" t="s">
-        <v>352</v>
+      <c r="D49" s="7" t="s">
+        <v>350</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="B50" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="C50" s="6" t="s">
+      <c r="C51" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="E51" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="9" t="s">
+    </row>
+    <row r="52" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="C51" s="6" t="s">
+      <c r="B52" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="C52" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>397</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>398</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>395</v>
-      </c>
     </row>
     <row r="53" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="9"/>
+      <c r="A53" s="8"/>
       <c r="B53" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="9" t="s">
-        <v>264</v>
+      <c r="A54" s="8" t="s">
+        <v>262</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>44</v>
@@ -4357,15 +4352,15 @@
         <v>85</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="9" t="s">
-        <v>372</v>
+      <c r="A55" s="8" t="s">
+        <v>370</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>86</v>
@@ -4374,56 +4369,56 @@
         <v>85</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="9"/>
+      <c r="A56" s="8"/>
       <c r="B56" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="9"/>
+      <c r="A57" s="8"/>
       <c r="B57" s="6" t="s">
         <v>45</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="9" t="s">
-        <v>273</v>
+      <c r="A58" s="8" t="s">
+        <v>271</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="9"/>
+      <c r="A59" s="8"/>
       <c r="B59" s="6" t="s">
         <v>47</v>
       </c>
@@ -4431,29 +4426,29 @@
         <v>92</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="9"/>
+      <c r="A60" s="8"/>
       <c r="B60" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>104</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="9"/>
+      <c r="A61" s="8"/>
       <c r="B61" s="6" t="s">
         <v>48</v>
       </c>
@@ -4461,15 +4456,15 @@
         <v>105</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="9" t="s">
-        <v>265</v>
+      <c r="A62" s="8" t="s">
+        <v>263</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>49</v>
@@ -4478,46 +4473,46 @@
         <v>76</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="9"/>
+      <c r="A63" s="8"/>
       <c r="B63" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C63" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E63" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="D63" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>411</v>
-      </c>
     </row>
     <row r="64" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="9" t="s">
-        <v>266</v>
+      <c r="A64" s="8" t="s">
+        <v>264</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="9"/>
+      <c r="A65" s="8"/>
       <c r="B65" s="6" t="s">
         <v>52</v>
       </c>
@@ -4525,31 +4520,31 @@
         <v>106</v>
       </c>
       <c r="D65" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="D66" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="E65" s="6" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>422</v>
-      </c>
       <c r="E66" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="9"/>
+      <c r="A67" s="8"/>
       <c r="B67" s="6" t="s">
         <v>53</v>
       </c>
@@ -4557,16 +4552,16 @@
         <v>107</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="9"/>
+      <c r="A68" s="8"/>
       <c r="B68" s="6" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>108</v>
@@ -4574,61 +4569,61 @@
       <c r="D68" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E68" s="7" t="s">
-        <v>512</v>
+      <c r="E68" s="6" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="8" t="s">
         <v>268</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="9" t="s">
-        <v>270</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="9"/>
+      <c r="A71" s="8"/>
       <c r="B71" s="6" t="s">
         <v>55</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>109</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="9"/>
+      <c r="A72" s="8"/>
       <c r="B72" s="6" t="s">
         <v>56</v>
       </c>
@@ -4637,12 +4632,12 @@
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="9" t="s">
-        <v>271</v>
+      <c r="A73" s="8" t="s">
+        <v>269</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>111</v>
@@ -4654,12 +4649,12 @@
         <v>120</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="9" t="s">
-        <v>272</v>
+      <c r="A74" s="8" t="s">
+        <v>270</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>112</v>
@@ -4675,8 +4670,8 @@
       </c>
     </row>
     <row r="75" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="9" t="s">
-        <v>274</v>
+      <c r="A75" s="8" t="s">
+        <v>272</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>114</v>
@@ -4685,49 +4680,49 @@
         <v>124</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="9" t="s">
-        <v>275</v>
+      <c r="A76" s="8" t="s">
+        <v>273</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>115</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>125</v>
+        <v>518</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="9" t="s">
-        <v>277</v>
+      <c r="A77" s="8" t="s">
+        <v>275</v>
       </c>
       <c r="B77" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="8" t="s">
         <v>276</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="9" t="s">
-        <v>278</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>116</v>
@@ -4736,15 +4731,15 @@
         <v>117</v>
       </c>
       <c r="D78" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="E78" s="6" t="s">
-        <v>496</v>
-      </c>
     </row>
     <row r="79" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="9" t="s">
-        <v>279</v>
+      <c r="A79" s="8" t="s">
+        <v>277</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>118</v>
@@ -4753,620 +4748,620 @@
         <v>119</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="9" t="s">
-        <v>280</v>
+      <c r="A80" s="8" t="s">
+        <v>278</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>66</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="9" t="s">
-        <v>282</v>
+      <c r="A81" s="8" t="s">
+        <v>280</v>
       </c>
       <c r="B81" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="8"/>
+      <c r="B82" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>490</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="9"/>
-      <c r="B82" s="6" t="s">
+      <c r="C82" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C82" s="6" t="s">
+      <c r="D82" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="E82" s="6" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="8"/>
+      <c r="B83" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="E82" s="6" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="9"/>
-      <c r="B83" s="6" t="s">
+      <c r="C83" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="9" t="s">
-        <v>283</v>
+      <c r="A84" s="8" t="s">
+        <v>281</v>
       </c>
       <c r="B84" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="B85" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C84" s="6" t="s">
+      <c r="C85" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="8"/>
+      <c r="B86" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C86" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="D84" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="9"/>
-      <c r="B86" s="6" t="s">
+      <c r="D86" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C86" s="6" t="s">
+      <c r="E86" s="6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="8"/>
+      <c r="B87" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C87" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D86" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="9"/>
-      <c r="B87" s="6" t="s">
+      <c r="D87" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C87" s="6" t="s">
+      <c r="E87" s="6" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="8"/>
+      <c r="B88" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C88" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="D87" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="9"/>
-      <c r="B88" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C88" s="6" t="s">
+      <c r="D88" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="D88" s="6" t="s">
-        <v>193</v>
-      </c>
       <c r="E88" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="9" t="s">
-        <v>266</v>
+      <c r="A89" s="8" t="s">
+        <v>264</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="9"/>
+      <c r="A90" s="8"/>
       <c r="B90" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="8"/>
+      <c r="B93" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="8"/>
+      <c r="B95" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="8"/>
+      <c r="B96" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="8"/>
+      <c r="B97" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E98" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C90" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>458</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="9"/>
-      <c r="B93" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="9" t="s">
+    </row>
+    <row r="99" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="8"/>
+      <c r="B99" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="8"/>
+      <c r="B100" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="8"/>
+      <c r="B101" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="B94" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="9"/>
-      <c r="B95" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="9"/>
-      <c r="B96" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="9"/>
-      <c r="B97" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="9" t="s">
+      <c r="B102" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="B98" s="6" t="s">
+      <c r="B104" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E104" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C98" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="9"/>
-      <c r="B99" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="9"/>
-      <c r="B100" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C100" s="6" t="s">
+    </row>
+    <row r="105" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="8"/>
+      <c r="B105" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="8"/>
+      <c r="B106" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="8"/>
+      <c r="B109" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D109" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="D100" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="9"/>
-      <c r="B101" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D102" s="6" t="s">
+      <c r="E109" s="6" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="8"/>
+      <c r="B110" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="8"/>
+      <c r="B114" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="C114" s="6" t="s">
         <v>440</v>
       </c>
-      <c r="E102" s="6" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="9" t="s">
-        <v>448</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="9"/>
-      <c r="B105" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="E105" s="6" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="9"/>
-      <c r="B106" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D106" s="6" t="s">
+      <c r="D114" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C116" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="E106" s="6" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="9"/>
-      <c r="B109" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="9"/>
-      <c r="B110" s="6" t="s">
-        <v>499</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E111" s="6" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="B112" s="6" t="s">
+      <c r="D116" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="8"/>
+      <c r="B117" s="6" t="s">
         <v>169</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D112" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="E112" s="6" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D113" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E113" s="6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="9"/>
-      <c r="B114" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="9"/>
-      <c r="B117" s="6" t="s">
-        <v>170</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="9"/>
+      <c r="A118" s="8"/>
       <c r="B118" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>60</v>
@@ -5375,15 +5370,15 @@
         <v>61</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="9" t="s">
-        <v>299</v>
+      <c r="A119" s="8" t="s">
+        <v>297</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>60</v>
@@ -5392,270 +5387,283 @@
         <v>61</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="9"/>
+      <c r="A120" s="8"/>
       <c r="B120" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="9"/>
+      <c r="A121" s="8"/>
       <c r="B121" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E121" s="6" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="8"/>
+      <c r="B122" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C122" s="6" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="9"/>
-      <c r="B122" s="6" t="s">
+      <c r="D122" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="8"/>
+      <c r="B123" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="D123" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C122" s="6" t="s">
+      <c r="E123" s="6" t="s">
         <v>481</v>
       </c>
-      <c r="D122" s="6" t="s">
+    </row>
+    <row r="124" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="8"/>
+      <c r="B124" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C124" s="6" t="s">
         <v>482</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="9"/>
-      <c r="B123" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>481</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E123" s="6" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="9"/>
-      <c r="B124" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>484</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>71</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="9" t="s">
-        <v>300</v>
+      <c r="A125" s="8" t="s">
+        <v>298</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>123</v>
       </c>
       <c r="D125" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="8"/>
+      <c r="B126" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C126" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="E125" s="6" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="9"/>
-      <c r="B126" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>71</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="9"/>
+      <c r="A127" s="8"/>
       <c r="B127" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>66</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="9"/>
+      <c r="A128" s="8"/>
       <c r="B128" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C128" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="D128" s="6"/>
       <c r="E128" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="9" t="s">
-        <v>301</v>
+      <c r="A129" s="8" t="s">
+        <v>299</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>70</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="9"/>
+      <c r="A130" s="8"/>
       <c r="B130" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="9" t="s">
-        <v>302</v>
+      <c r="A131" s="8" t="s">
+        <v>300</v>
       </c>
       <c r="B131" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="8"/>
+      <c r="B132" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="C131" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="9"/>
-      <c r="B132" s="6" t="s">
-        <v>216</v>
-      </c>
       <c r="C132" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>109</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="9"/>
+      <c r="A133" s="8"/>
       <c r="B133" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C133" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="D133" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D133" s="6" t="s">
-        <v>219</v>
-      </c>
       <c r="E133" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="9"/>
+      <c r="A134" s="8"/>
       <c r="B134" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C134" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>65</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="9" t="s">
-        <v>235</v>
+      <c r="A135" s="8" t="s">
+        <v>234</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="9" t="s">
+      <c r="A136" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="6"/>
+      <c r="B137" s="6" t="s">
         <v>515</v>
       </c>
-      <c r="B136" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="C136" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="D136" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>514</v>
+      <c r="C137" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="D137" s="6"/>
+      <c r="E137" s="6" t="s">
+        <v>516</v>
       </c>
     </row>
   </sheetData>

--- a/src/CQs.xlsx
+++ b/src/CQs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A673ED-72EA-4A53-BB6D-7B7DEBACEE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82BA4612-2FD2-41EF-9FA3-BE7008588C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CQs" sheetId="1" r:id="rId1"/>
@@ -1066,9 +1066,6 @@
     <t>Which works share the same combination of textual features?</t>
   </si>
   <si>
-    <t>Which textual features are exclusively associated with works published before 1900?</t>
-  </si>
-  <si>
     <t>Which narrator types are most frequent in the corpus?</t>
   </si>
   <si>
@@ -1706,25 +1703,6 @@
 }
 GROUP BY ?feature
 ORDER BY DESC(?nb)</t>
-  </si>
-  <si>
-    <t>SELECT DISTINCT ?feature WHERE {
-  ?feature a gc:G18_Textual_Feature .
-  FILTER EXISTS {
-    ?work a lrm:F1_Work ; 
-          gc:GP0_has_feature ?feature .
-    ?expr a lrm:F2_Expression ;
-          dcterms:issued ?date .
-    FILTER(xsd:integer(str(?date)) &lt; 1900)
-  }
-  FILTER NOT EXISTS {
-    ?work2 a lrm:F1_Work ; 
-           gc:GP0_has_feature ?feature .
-    ?expr a lrm:F2_Expression ;
-          dcterms:issued ?date2 .
-    FILTER(xsd:integer(str(?date2)) &gt;= 1900)
-  }
-}</t>
   </si>
   <si>
     <t>lrm:F1_Work ; gc:G18_Textual_Feature ; lrm:F2_Expression</t>
@@ -3042,6 +3020,31 @@
   </si>
   <si>
     <t>lrm:F1_Work ; gc:G12_Setting ; crm:E55_Type</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT ?feature WHERE {
+  ?feature a gc:G18_Textual_Feature .
+  FILTER(?feature != sf:Feature_science_fiction_genre)
+  FILTER EXISTS {
+    ?work a lrm:F1_Work ; 
+          gc:GP0_has_feature ?feature .
+    ?expr a lrm:F2_Expression ;
+          lrm:R3i_realises ?work ;
+          dcterms:issued ?date .
+    FILTER(xsd:integer(str(?date)) &lt; 1900)
+  }
+  FILTER NOT EXISTS {
+    ?work2 a lrm:F1_Work ; 
+           gc:GP0_has_feature ?feature .
+    ?expr a lrm:F2_Expression ;
+          lrm:R3i_realises ?work2 ;
+          dcterms:issued ?date2 .
+    FILTER(xsd:integer(str(?date2)) &gt;= 1900)
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which textual features are exclusively associated with works published before 1900 (except for "science fiction feature")?</t>
   </si>
 </sst>
 </file>
@@ -3469,7 +3472,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -3487,7 +3490,7 @@
     </row>
     <row r="2" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
@@ -3505,25 +3508,25 @@
     </row>
     <row r="3" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>307</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>308</v>
       </c>
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>5</v>
@@ -3532,39 +3535,39 @@
         <v>63</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>311</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>59</v>
@@ -3585,7 +3588,7 @@
         <v>61</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3597,27 +3600,27 @@
         <v>75</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3635,7 +3638,7 @@
     </row>
     <row r="11" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>11</v>
@@ -3647,22 +3650,22 @@
         <v>59</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>109</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G12" s="3"/>
     </row>
@@ -3678,13 +3681,13 @@
         <v>67</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="6" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>78</v>
@@ -3693,24 +3696,24 @@
         <v>68</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3725,12 +3728,12 @@
         <v>69</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>12</v>
@@ -3742,12 +3745,12 @@
         <v>58</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>16</v>
@@ -3759,46 +3762,46 @@
         <v>58</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>80</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>17</v>
@@ -3810,12 +3813,12 @@
         <v>70</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="5" customFormat="1" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>27</v>
@@ -3824,16 +3827,16 @@
         <v>84</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F22" s="12"/>
     </row>
     <row r="23" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>19</v>
@@ -3845,12 +3848,12 @@
         <v>85</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>20</v>
@@ -3859,15 +3862,15 @@
         <v>87</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>21</v>
@@ -3876,18 +3879,18 @@
         <v>88</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>82</v>
@@ -3896,13 +3899,13 @@
         <v>89</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>23</v>
@@ -3911,16 +3914,16 @@
         <v>76</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>24</v>
@@ -3929,16 +3932,16 @@
         <v>90</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>25</v>
@@ -3947,33 +3950,33 @@
         <v>76</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>87</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>34</v>
@@ -3982,33 +3985,33 @@
         <v>92</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>91</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>26</v>
@@ -4020,41 +4023,41 @@
         <v>70</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>93</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>93</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4069,7 +4072,7 @@
         <v>71</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4082,7 +4085,7 @@
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4094,10 +4097,10 @@
         <v>78</v>
       </c>
       <c r="D38" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="E38" s="6" t="s">
         <v>343</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4127,7 +4130,7 @@
         <v>73</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4140,7 +4143,7 @@
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4152,10 +4155,10 @@
         <v>97</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F42" s="13"/>
     </row>
@@ -4171,24 +4174,24 @@
         <v>70</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>254</v>
-      </c>
       <c r="C44" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4208,10 +4211,10 @@
     </row>
     <row r="46" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>302</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>303</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>99</v>
@@ -4220,7 +4223,7 @@
         <v>100</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4240,7 +4243,7 @@
     </row>
     <row r="48" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>42</v>
@@ -4252,12 +4255,12 @@
         <v>102</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>9</v>
@@ -4266,61 +4269,61 @@
         <v>103</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>260</v>
-      </c>
       <c r="C51" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4329,18 +4332,18 @@
         <v>43</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>44</v>
@@ -4352,15 +4355,15 @@
         <v>85</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>86</v>
@@ -4369,7 +4372,7 @@
         <v>85</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4384,7 +4387,7 @@
         <v>136</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4393,28 +4396,28 @@
         <v>45</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4426,25 +4429,25 @@
         <v>92</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>
       <c r="B60" s="6" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>104</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4456,15 +4459,15 @@
         <v>105</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>49</v>
@@ -4473,10 +4476,10 @@
         <v>76</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4485,30 +4488,30 @@
         <v>50</v>
       </c>
       <c r="C63" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="E63" s="6" t="s">
         <v>407</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>408</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4520,27 +4523,27 @@
         <v>106</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>175</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4552,16 +4555,16 @@
         <v>107</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
       <c r="B68" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>108</v>
@@ -4570,41 +4573,41 @@
         <v>109</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B69" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B69" s="6" t="s">
-        <v>267</v>
-      </c>
       <c r="C69" s="6" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4613,13 +4616,13 @@
         <v>55</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>109</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4632,12 +4635,12 @@
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>111</v>
@@ -4649,12 +4652,12 @@
         <v>120</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>112</v>
@@ -4671,7 +4674,7 @@
     </row>
     <row r="75" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>114</v>
@@ -4680,49 +4683,49 @@
         <v>124</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>115</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>116</v>
@@ -4731,15 +4734,15 @@
         <v>117</v>
       </c>
       <c r="D78" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>492</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>118</v>
@@ -4748,44 +4751,44 @@
         <v>119</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="B80" s="6" t="s">
-        <v>279</v>
-      </c>
       <c r="C80" s="6" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>66</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4800,7 +4803,7 @@
         <v>129</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4813,12 +4816,12 @@
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>132</v>
@@ -4830,12 +4833,12 @@
         <v>134</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>133</v>
@@ -4847,7 +4850,7 @@
         <v>134</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4862,7 +4865,7 @@
         <v>136</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4877,7 +4880,7 @@
         <v>138</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4892,24 +4895,24 @@
         <v>192</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4924,29 +4927,29 @@
         <v>138</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>142</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>193</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>143</v>
@@ -4958,7 +4961,7 @@
         <v>195</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4973,12 +4976,12 @@
         <v>145</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>146</v>
@@ -4990,7 +4993,7 @@
         <v>195</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5005,7 +5008,7 @@
         <v>148</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5020,7 +5023,7 @@
         <v>145</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5035,12 +5038,12 @@
         <v>151</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>152</v>
@@ -5058,16 +5061,16 @@
     <row r="99" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="8"/>
       <c r="B99" s="6" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C99" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="E99" s="6" t="s">
         <v>501</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5091,18 +5094,18 @@
         <v>154</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>155</v>
@@ -5111,18 +5114,18 @@
         <v>202</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>203</v>
@@ -5131,12 +5134,12 @@
         <v>201</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>162</v>
@@ -5163,7 +5166,7 @@
         <v>204</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5178,12 +5181,12 @@
         <v>206</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>160</v>
@@ -5192,15 +5195,15 @@
         <v>202</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>161</v>
@@ -5209,10 +5212,10 @@
         <v>202</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5227,13 +5230,13 @@
         <v>201</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="8"/>
       <c r="B110" s="6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>207</v>
@@ -5242,12 +5245,12 @@
         <v>201</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>164</v>
@@ -5259,12 +5262,12 @@
         <v>201</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>168</v>
@@ -5276,12 +5279,12 @@
         <v>209</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>167</v>
@@ -5293,27 +5296,27 @@
         <v>210</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="8"/>
       <c r="B114" s="6" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>210</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>165</v>
@@ -5322,15 +5325,15 @@
         <v>211</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>166</v>
@@ -5342,7 +5345,7 @@
         <v>212</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5361,7 +5364,7 @@
     <row r="118" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="8"/>
       <c r="B118" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>60</v>
@@ -5375,7 +5378,7 @@
     </row>
     <row r="119" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>170</v>
@@ -5387,7 +5390,7 @@
         <v>61</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5399,10 +5402,10 @@
         <v>77</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5417,7 +5420,7 @@
         <v>138</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5426,13 +5429,13 @@
         <v>177</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5441,13 +5444,13 @@
         <v>179</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>178</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5456,18 +5459,18 @@
         <v>180</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>71</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>181</v>
@@ -5479,7 +5482,7 @@
         <v>184</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5500,16 +5503,16 @@
     <row r="127" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="8"/>
       <c r="B127" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>66</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5522,24 +5525,24 @@
       </c>
       <c r="D128" s="6"/>
       <c r="E128" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>70</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5548,100 +5551,100 @@
         <v>213</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>59</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>214</v>
+        <v>518</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>355</v>
+        <v>517</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="8"/>
       <c r="B132" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>109</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="8"/>
       <c r="B133" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C133" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="C133" s="6" t="s">
+      <c r="D133" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="D133" s="6" t="s">
-        <v>218</v>
-      </c>
       <c r="E133" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="8"/>
       <c r="B134" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C134" s="6" t="s">
         <v>227</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>65</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>194</v>
@@ -5650,20 +5653,20 @@
         <v>195</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6"/>
       <c r="B137" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C137" s="6" t="s">
         <v>515</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>517</v>
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="6" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>

--- a/src/CQs.xlsx
+++ b/src/CQs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82BA4612-2FD2-41EF-9FA3-BE7008588C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53E646D-FC51-4F7F-B629-F37DB09212C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="CQs" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CQs!$C$1:$C$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CQs!$C$1:$C$136</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="518">
   <si>
     <t>CQ</t>
   </si>
@@ -376,9 +376,6 @@
     </r>
   </si>
   <si>
-    <t>How many members are there in each community?</t>
-  </si>
-  <si>
     <t>What narrative locations appear in the corpus?</t>
   </si>
   <si>
@@ -552,15 +549,9 @@
     <t>crm:P67i_is_referred_to_by</t>
   </si>
   <si>
-    <t>dul:hasMember</t>
-  </si>
-  <si>
     <t>gc:G13_Narrative_Location</t>
   </si>
   <si>
-    <t>dul:hasLocation</t>
-  </si>
-  <si>
     <t>gc:G5_Narrative_Event</t>
   </si>
   <si>
@@ -618,16 +609,7 @@
     <t>gc:G9_Narrative_Unit ; gc:G10_Narrative_Function</t>
   </si>
   <si>
-    <t>dul:Community ; gc:G1_Character</t>
-  </si>
-  <si>
     <t>gc:G13_Narrative_Location ; crm:E55_Type</t>
-  </si>
-  <si>
-    <t>dul:Organization ; gc:G13_Narrative_Location</t>
-  </si>
-  <si>
-    <t>gc:G1_Character ; gc:G13_Narrative_Location ; dul:Organization ; dul:Community ; sf:H1_Conceptual_Novum ; sf:H2_Concrete_Novum</t>
   </si>
   <si>
     <t>sf:H1_Conceptual_Novum ; sf:H2_Concrete_Novum ; gc:G0_Character-Stoff ; gc:G1_Character</t>
@@ -720,9 +702,6 @@
   </si>
   <si>
     <t>lrm:F1_Work ; gc:G0_Character-Stoff</t>
-  </si>
-  <si>
-    <t>dul:Organization</t>
   </si>
   <si>
     <t>Which character archetypes evolved from antagonist to protagonist across different works?</t>
@@ -954,38 +933,16 @@
     <t>Which narrative events occur within the same time-interval?</t>
   </si>
   <si>
-    <t>Which communities and organizations include non-human characters?</t>
-  </si>
-  <si>
     <t>Which narrative locations appear in works published between 1880 and 1900?</t>
   </si>
   <si>
-    <t>SELECT ?org ?label WHERE {
-  ?org a dul:Organization .
-  OPTIONAL { ?org rdfs:label ?label . }
-  FILTER EXISTS {
-    ?org dul:hasMember ?member .
-  }
-  FILTER NOT EXISTS {
-    ?org dul:hasMember ?member .
-    FILTER NOT EXISTS { ?member a sf:H3_Human_Character . }
-  }
-}</t>
-  </si>
-  <si>
     <t>Which organizations contain only human characters?</t>
   </si>
   <si>
     <t>dcterms:issued ; crm:P67i_is_referred_to_by</t>
   </si>
   <si>
-    <t>dul:Organization ; sf:H3_Human_Character</t>
-  </si>
-  <si>
     <t>Which groups are present in the corpus?</t>
-  </si>
-  <si>
-    <t>dul:Group</t>
   </si>
   <si>
     <t>gc:G3_Psychological_State ; gc:G1_Characters</t>
@@ -1177,9 +1134,6 @@
   </si>
   <si>
     <t>Which communities does [G1_Character] belong to?</t>
-  </si>
-  <si>
-    <t>Who are the members of the [Organization/Community]?</t>
   </si>
   <si>
     <t>Which features are shared by more than [number] works?</t>
@@ -1516,15 +1470,8 @@
     <t>gc:GP1_is_character_in ; dlpext:plays</t>
   </si>
   <si>
-    <t>SELECT ?org ?label WHERE {   
-  ?org a dul:Organization ;        
-         crm:P67i_is_referred_to_by sf:Work_LHomme_Bicycle ;        
-         rdfs:label ?label .   
-}</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Which communities does Marius belong to in </t>
+    <r>
+      <t xml:space="preserve">Who are the members of the bicycle-man race in </t>
     </r>
     <r>
       <rPr>
@@ -1545,55 +1492,6 @@
     </r>
   </si>
   <si>
-    <t>SELECT ?community WHERE {   
-  ?community a dul:Community ;              
-               dul:hasMember sf:Marius .
-  sf:Marius gc:GP1_is_character_in sf:Work_LHomme_Bicycle .             
-}</t>
-  </si>
-  <si>
-    <t>dul:hasMember ; gc:GP1_is_character_in</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Who are the members of the bicycle-man race in </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Homme-bicycle</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>?</t>
-    </r>
-  </si>
-  <si>
-    <t>SELECT ?member WHERE {   
-  sf:Bicycle_men_race dul:hasMember ?member ;
-        crm:P67i_is_referred_to_by sf:Work_LHomme_Bicycle .  
-}</t>
-  </si>
-  <si>
-    <t>SELECT ?community (COUNT(?member) AS ?nb) WHERE {   
-  ?community a dul:Community ;              
-               dul:hasMember ?member . 
-} 
-GROUP BY ?community 
-ORDER BY DESC(?nb)</t>
-  </si>
-  <si>
-    <t>dul:hasMember ; crm:P67i_is_referred_to_by</t>
-  </si>
-  <si>
     <t>SELECT ?loc WHERE {   
   ?loc a gc:G13_Narrative_Location .
 }</t>
@@ -1607,38 +1505,6 @@
          crm:P67_refers_to ?real . 
   ?real a dlpcom:geographical-place .
 }</t>
-  </si>
-  <si>
-    <t>SELECT ?org ?loc WHERE {   
-  ?org a dul:Organization ;        
-         dul:hasLocation ?loc . 
-}</t>
-  </si>
-  <si>
-    <t>SELECT ?type (COUNT(?entity) AS ?nb) WHERE {   
-  { ?entity a gc:G1_Character .     
-    BIND("Character" AS ?type) 
-  }   
-  UNION   
-  { ?entity a gc:G13_Narrative_Location . 
-    BIND("Location" AS ?type) 
-  }   
-  UNION   
-  { ?entity a dul:Organization .     
-    BIND("Organization" AS ?type) 
-  }   
-  UNION   
-  { ?entity a dul:Community .     
-    BIND("Community" AS ?type) 
-  } 
-  UNION
-  { ?entity a ?novumClass .
-    FILTER (?novumClass IN (sf:H1_Conceptual_Novum, sf:H2_Concrete_Novum))
-    BIND("Novum" AS ?type)
-  }
-} 
-GROUP BY ?type 
-ORDER BY DESC(?nb)</t>
   </si>
   <si>
     <t>SELECT ?expr ?date WHERE {   
@@ -1712,23 +1578,6 @@
   </si>
   <si>
     <t>Which Organization are referenced in more than one work?</t>
-  </si>
-  <si>
-    <t>lrm:F1_Work ; dul:Organization</t>
-  </si>
-  <si>
-    <t>SELECT ?group (COUNT(DISTINCT ?work) AS ?nb) WHERE {
-  ?group a dul:Organization ;
-         crm:P67i_is_referred_to_by ?work .
-}
-GROUP BY ?group
-HAVING (COUNT(DISTINCT ?work) &gt; 1)
-ORDER BY DESC(?nb)</t>
-  </si>
-  <si>
-    <t>SELECT ?group WHERE {
-  ?group a dul:Group .
-}</t>
   </si>
   <si>
     <t>SELECT ?year (COUNT(DISTINCT ?work) AS ?nb_works) WHERE {
@@ -2717,20 +2566,6 @@
 HAVING (COUNT(DISTINCT ?event) &gt; 1)</t>
   </si>
   <si>
-    <t>dul:Organization ; sf:H4_Non-human_Character ; dul:Community</t>
-  </si>
-  <si>
-    <t>SELECT ?group WHERE {
-  { ?group a dul:Community . } UNION { ?group a dul:Organization . }
-  ?group dul:hasMember ?char .
-  FILTER EXISTS {
-    ?group dul:hasMember ?nonhuman .
-    ?nonhuman a sf:H4_Non-human_Character .
-  }
-}
-GROUP BY ?group</t>
-  </si>
-  <si>
     <t>How does the distribution of psychological traits evolve across publication decades?</t>
   </si>
   <si>
@@ -2767,16 +2602,7 @@
     <t>gc:G0_Character-Stoff ; lrm:F1_Work ; gc:G1_Character</t>
   </si>
   <si>
-    <t>SELECT ?org WHERE {
-  ?org a dul:Organization ;
-       crm:P2_has_type sf:type_academic_institution .
-}</t>
-  </si>
-  <si>
     <t>dcterms:creator ; dlpext:plays ; dlpfun:state-of ; crm:P2_has_type</t>
-  </si>
-  <si>
-    <t>dul:Organization ; E55_Type</t>
   </si>
   <si>
     <t>dcterms:creator ; gc:GP1_is_character_in ; dlpext:plays</t>
@@ -3045,6 +2871,172 @@
   </si>
   <si>
     <t>Which textual features are exclusively associated with works published before 1900 (except for "science fiction feature")?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Which organizations does Marius belong to in </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Homme-bicycle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>sf:H8_Organization ; gc:G1_Character</t>
+  </si>
+  <si>
+    <t>sf:H9_Collective ; gc:G1_Character</t>
+  </si>
+  <si>
+    <t>Who are the members of the [Organization]?</t>
+  </si>
+  <si>
+    <t>gc:G1_Character ; gc:G13_Narrative_Location ; sf:H8_Organization ; sf:H9_Collective ; sf:H1_Conceptual_Novum ; sf:H2_Concrete_Novum</t>
+  </si>
+  <si>
+    <t>SELECT ?type (COUNT(?entity) AS ?nb) WHERE {   
+  { ?entity a gc:G1_Character .     
+    BIND("Character" AS ?type) 
+  }   
+  UNION   
+  { ?entity a gc:G13_Narrative_Location . 
+    BIND("Location" AS ?type) 
+  }   
+  UNION   
+  { ?entity a sf:H8_Organization .     
+    BIND("Organization" AS ?type) 
+  }   
+  UNION   
+  { ?entity a sf:H9_Collective .     
+    BIND("Collective" AS ?type) 
+  } 
+  UNION
+  { ?entity a ?novumClass .
+    FILTER (?novumClass IN (sf:H1_Conceptual_Novum, sf:H2_Concrete_Novum))
+    BIND("Novum" AS ?type)
+  }
+} 
+GROUP BY ?type 
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>Which organizations include non-human characters?</t>
+  </si>
+  <si>
+    <t>sf:H9_Collective</t>
+  </si>
+  <si>
+    <t>SELECT ?group WHERE {
+  ?group a sf:H9_Group .
+}</t>
+  </si>
+  <si>
+    <t>sf:H8_Organization</t>
+  </si>
+  <si>
+    <t>SELECT ?org ?label WHERE {   
+  ?org a sf:H8_Organization ;        
+         crm:P67i_is_referred_to_by sf:Work_LHomme_Bicycle ;        
+         rdfs:label ?label .   
+}</t>
+  </si>
+  <si>
+    <t>sf:H8_Organization ; E55_Type</t>
+  </si>
+  <si>
+    <t>SELECT ?org WHERE {
+  ?org a sf:H8_Organization ;
+       crm:P2_has_type sf:type_academic_institution .
+}</t>
+  </si>
+  <si>
+    <t>sf:H8_Organization ; sf:H4_Non-human_Character</t>
+  </si>
+  <si>
+    <t>sf:H8_Organization ; sf:H3_Human_Character</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; sf:H8_Organization</t>
+  </si>
+  <si>
+    <t>SELECT ?group (COUNT(DISTINCT ?work) AS ?nb) WHERE {
+  ?group a sf:H8_Organization ;
+         crm:P67i_is_referred_to_by ?work .
+}
+GROUP BY ?group
+HAVING (COUNT(DISTINCT ?work) &gt; 1)
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>sf:HP10_has_member</t>
+  </si>
+  <si>
+    <t>SELECT ?org WHERE {   
+  ?org a sf:H8_Organization ;              
+               sf:H¨10_has_member sf:Marius .
+  sf:Marius gc:GP1_is_character_in sf:Work_LHomme_Bicycle .             
+}</t>
+  </si>
+  <si>
+    <t>sf:HP10_has_member ; crm:P67i_is_referred_to_by</t>
+  </si>
+  <si>
+    <t>sf:HP10_has_member ; gc:GP1_is_character_in</t>
+  </si>
+  <si>
+    <t>SELECT ?member WHERE {   
+  sf:Bicycle_men_race sf:HP10_has_member ?member ;
+        crm:P67i_is_referred_to_by sf:Work_LHomme_Bicycle .  
+}</t>
+  </si>
+  <si>
+    <t>SELECT ?group WHERE {
+  { ?group a sf:H8_Organization . }
+  ?group sf:HP10_has_member ?char .
+  FILTER EXISTS {
+    ?group sf:HP10_has_member ?nonhuman .
+    ?nonhuman a sf:H4_Non-human_Character .
+  }
+}
+GROUP BY ?group</t>
+  </si>
+  <si>
+    <t>SELECT ?org ?label WHERE {
+  ?org a sf:H8_Organization .
+  OPTIONAL { ?org rdfs:label ?label . }
+  FILTER EXISTS {
+    ?org sf:HP10_has_member ?member .
+  }
+  FILTER NOT EXISTS {
+    ?org sf:HP10_has_member ?member .
+    FILTER NOT EXISTS { ?member a sf:H3_Human_Character . }
+  }
+}</t>
+  </si>
+  <si>
+    <t>sf:HP13_has_location</t>
+  </si>
+  <si>
+    <t>SELECT ?org ?loc WHERE {   
+  ?org a sf:H9_Organization ;        
+         sf:HP13_has_location ?loc . 
+}</t>
+  </si>
+  <si>
+    <t>sf:H8_Organization ; gc:G13_Narrative_Location</t>
   </si>
 </sst>
 </file>
@@ -3460,7 +3452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="43.77734375" style="10" customWidth="1"/>
@@ -3472,7 +3464,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -3481,7 +3473,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>1</v>
@@ -3490,16 +3482,16 @@
     </row>
     <row r="2" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>15</v>
@@ -3508,69 +3500,69 @@
     </row>
     <row r="3" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="G3" s="2"/>
     </row>
     <row r="4" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="G4" s="2"/>
     </row>
     <row r="5" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>14</v>
@@ -3582,45 +3574,45 @@
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="E7" s="6" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3629,7 +3621,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
@@ -3638,34 +3630,34 @@
     </row>
     <row r="11" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="6" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>369</v>
+        <v>345</v>
       </c>
       <c r="G12" s="3"/>
     </row>
@@ -3675,45 +3667,45 @@
         <v>3</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>370</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="6" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>371</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>372</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3722,342 +3714,342 @@
         <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>373</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>374</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>375</v>
+        <v>351</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>377</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>380</v>
+        <v>356</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>379</v>
+        <v>355</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="5" customFormat="1" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>27</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="F22" s="12"/>
     </row>
     <row r="23" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="G26" s="5"/>
     </row>
     <row r="27" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="G27" s="5"/>
     </row>
     <row r="28" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="G30" s="5"/>
     </row>
     <row r="31" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>366</v>
+        <v>342</v>
       </c>
       <c r="G31" s="5"/>
     </row>
     <row r="32" spans="1:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>125</v>
+        <v>500</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>333</v>
+        <v>501</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>334</v>
+        <v>491</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>93</v>
+        <v>492</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>336</v>
+        <v>511</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>335</v>
+        <v>509</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>251</v>
+        <v>494</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>93</v>
+        <v>493</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>340</v>
+        <v>510</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>338</v>
+        <v>512</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4066,13 +4058,11 @@
         <v>28</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>71</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="D36" s="6"/>
       <c r="E36" s="6" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4081,11 +4071,13 @@
         <v>29</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D37" s="6"/>
+        <v>75</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>323</v>
+      </c>
       <c r="E37" s="6" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4094,13 +4086,13 @@
         <v>30</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>342</v>
+        <v>65</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>343</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4109,13 +4101,13 @@
         <v>31</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>94</v>
+        <v>517</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>66</v>
+        <v>515</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>22</v>
+        <v>516</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4124,27 +4116,28 @@
         <v>32</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>73</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>344</v>
+        <v>496</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="D41" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>443</v>
+      </c>
       <c r="E41" s="6" t="s">
-        <v>345</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="F41" s="13"/>
     </row>
     <row r="42" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
@@ -4152,462 +4145,461 @@
         <v>36</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>467</v>
+        <v>69</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>466</v>
-      </c>
-      <c r="F42" s="13"/>
+        <v>358</v>
+      </c>
     </row>
     <row r="43" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
+      <c r="A43" s="8" t="s">
+        <v>240</v>
+      </c>
       <c r="B43" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="8"/>
+      <c r="B44" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="D44" s="6" t="s">
+    </row>
+    <row r="45" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="8"/>
+      <c r="B46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="6" t="s">
+      <c r="D46" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="C47" s="6" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>40</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>102</v>
+        <v>9</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>349</v>
+        <v>244</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>362</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>384</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>259</v>
+        <v>366</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="8" t="s">
-        <v>260</v>
-      </c>
+      <c r="A52" s="8"/>
       <c r="B52" s="6" t="s">
-        <v>390</v>
+        <v>42</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>393</v>
+        <v>371</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
+      <c r="A53" s="8" t="s">
+        <v>249</v>
+      </c>
       <c r="B53" s="6" t="s">
         <v>43</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>395</v>
+        <v>83</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>396</v>
+        <v>82</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>392</v>
+        <v>441</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
-        <v>261</v>
+        <v>344</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>44</v>
+        <v>343</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>465</v>
+        <v>373</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="8" t="s">
-        <v>368</v>
-      </c>
+      <c r="A55" s="8"/>
       <c r="B55" s="6" t="s">
-        <v>367</v>
+        <v>167</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>85</v>
+        <v>129</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>397</v>
+        <v>449</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="6" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>136</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>473</v>
+        <v>374</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
+      <c r="A57" s="8" t="s">
+        <v>258</v>
+      </c>
       <c r="B57" s="6" t="s">
         <v>45</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>399</v>
-      </c>
-      <c r="D57" s="6"/>
+        <v>479</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>478</v>
+      </c>
       <c r="E57" s="6" t="s">
-        <v>398</v>
+        <v>477</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="8" t="s">
-        <v>270</v>
-      </c>
+      <c r="A58" s="8"/>
       <c r="B58" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>507</v>
+        <v>89</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>506</v>
+        <v>312</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>505</v>
+        <v>376</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8"/>
       <c r="B59" s="6" t="s">
-        <v>47</v>
+        <v>377</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>324</v>
+        <v>379</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>
       <c r="B60" s="6" t="s">
-        <v>401</v>
+        <v>47</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>403</v>
+        <v>320</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
+      <c r="A61" s="8" t="s">
+        <v>250</v>
+      </c>
       <c r="B61" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>411</v>
+        <v>380</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="8" t="s">
-        <v>262</v>
-      </c>
+      <c r="A62" s="8"/>
       <c r="B62" s="6" t="s">
         <v>49</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>76</v>
+        <v>381</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>324</v>
+        <v>382</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
+      <c r="A63" s="8" t="s">
+        <v>251</v>
+      </c>
       <c r="B63" s="6" t="s">
         <v>50</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="8" t="s">
-        <v>263</v>
-      </c>
+      <c r="A64" s="8"/>
       <c r="B64" s="6" t="s">
         <v>51</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>414</v>
+        <v>100</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
+      <c r="A65" s="8" t="s">
+        <v>252</v>
+      </c>
       <c r="B65" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="8"/>
+      <c r="B66" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C65" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>416</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="8" t="s">
-        <v>264</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>175</v>
-      </c>
       <c r="C66" s="6" t="s">
-        <v>417</v>
+        <v>101</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>
       <c r="B67" s="6" t="s">
-        <v>53</v>
+        <v>288</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>420</v>
+        <v>103</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>419</v>
+        <v>484</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
+      <c r="A68" s="8" t="s">
+        <v>253</v>
+      </c>
       <c r="B68" s="6" t="s">
-        <v>300</v>
+        <v>254</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>108</v>
+        <v>398</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>109</v>
+        <v>318</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>512</v>
+        <v>397</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>266</v>
+        <v>53</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>422</v>
+        <v>205</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>330</v>
+        <v>58</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>421</v>
+        <v>399</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="8" t="s">
-        <v>267</v>
-      </c>
+      <c r="A70" s="8"/>
       <c r="B70" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>216</v>
+        <v>401</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>423</v>
+        <v>400</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4616,980 +4608,980 @@
         <v>55</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>109</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D71" s="6"/>
       <c r="E71" s="6" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
+      <c r="A72" s="8" t="s">
+        <v>256</v>
+      </c>
       <c r="B72" s="6" t="s">
-        <v>56</v>
+        <v>105</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D72" s="6"/>
+        <v>80</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>114</v>
+      </c>
       <c r="E72" s="6" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>427</v>
+        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>113</v>
+        <v>404</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>124</v>
+        <v>488</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>429</v>
+        <v>406</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>428</v>
+        <v>386</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>115</v>
+        <v>261</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>516</v>
+        <v>294</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>410</v>
+        <v>465</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>273</v>
+        <v>110</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>306</v>
+        <v>111</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>494</v>
+        <v>462</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>493</v>
+        <v>464</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="8" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>490</v>
+        <v>461</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>492</v>
+        <v>463</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="8" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>118</v>
+        <v>266</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>119</v>
+        <v>502</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>488</v>
+        <v>65</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>278</v>
+        <v>119</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>489</v>
+        <v>460</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>66</v>
+        <v>459</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>487</v>
+        <v>458</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="8" t="s">
-        <v>279</v>
-      </c>
+      <c r="A81" s="8"/>
       <c r="B81" s="6" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>486</v>
+        <v>121</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>485</v>
+        <v>122</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
       <c r="B82" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D83" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="8"/>
-      <c r="B83" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="D83" s="6"/>
       <c r="E83" s="6" t="s">
-        <v>461</v>
+        <v>436</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>460</v>
+        <v>435</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="8" t="s">
-        <v>281</v>
-      </c>
+      <c r="A85" s="8"/>
       <c r="B85" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="8"/>
       <c r="B86" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>458</v>
+        <v>433</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="8"/>
       <c r="B87" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>138</v>
+        <v>181</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>457</v>
+        <v>432</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="8"/>
+      <c r="A88" s="8" t="s">
+        <v>251</v>
+      </c>
       <c r="B88" s="6" t="s">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>191</v>
+        <v>431</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>192</v>
+        <v>389</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>456</v>
+        <v>388</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="8" t="s">
-        <v>263</v>
-      </c>
+      <c r="A89" s="8"/>
       <c r="B89" s="6" t="s">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>455</v>
+        <v>179</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>413</v>
+        <v>131</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="8"/>
+      <c r="A90" s="8" t="s">
+        <v>270</v>
+      </c>
       <c r="B90" s="6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>190</v>
+        <v>430</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>504</v>
+        <v>429</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>454</v>
+        <v>183</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>453</v>
+        <v>428</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="8" t="s">
-        <v>283</v>
-      </c>
+      <c r="A92" s="8"/>
       <c r="B92" s="6" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>452</v>
+        <v>427</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="8"/>
+      <c r="A93" s="8" t="s">
+        <v>272</v>
+      </c>
       <c r="B93" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>451</v>
+        <v>426</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="8" t="s">
-        <v>284</v>
-      </c>
+      <c r="A94" s="8"/>
       <c r="B94" s="6" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>195</v>
+        <v>141</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>450</v>
+        <v>425</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="8"/>
       <c r="B95" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="8"/>
       <c r="B96" s="6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D96" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B97" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E96" s="6" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="8"/>
-      <c r="B97" s="6" t="s">
-        <v>150</v>
-      </c>
       <c r="C97" s="6" t="s">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>448</v>
+        <v>134</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="8" t="s">
-        <v>285</v>
-      </c>
+      <c r="A98" s="8"/>
       <c r="B98" s="6" t="s">
-        <v>152</v>
+        <v>423</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>194</v>
+        <v>471</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>195</v>
+        <v>472</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>141</v>
+        <v>473</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="8"/>
       <c r="B99" s="6" t="s">
-        <v>447</v>
+        <v>150</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>499</v>
+        <v>189</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>501</v>
+        <v>151</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="8"/>
       <c r="B100" s="6" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>200</v>
+        <v>471</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>201</v>
+        <v>472</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>158</v>
+        <v>470</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="8"/>
+      <c r="A101" s="8" t="s">
+        <v>274</v>
+      </c>
       <c r="B101" s="6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>499</v>
+        <v>191</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>500</v>
+        <v>412</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>498</v>
+        <v>422</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
-        <v>286</v>
+        <v>420</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>155</v>
+        <v>419</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>436</v>
+        <v>190</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>446</v>
+        <v>421</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
-        <v>444</v>
+        <v>275</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>443</v>
+        <v>155</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>445</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="8" t="s">
-        <v>287</v>
-      </c>
+      <c r="A104" s="8"/>
       <c r="B104" s="6" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>153</v>
+        <v>418</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="8"/>
       <c r="B105" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="8"/>
+      <c r="A106" s="8" t="s">
+        <v>276</v>
+      </c>
       <c r="B106" s="6" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>206</v>
+        <v>412</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>441</v>
+        <v>416</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>440</v>
+        <v>415</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="8" t="s">
-        <v>289</v>
-      </c>
+      <c r="A108" s="8"/>
       <c r="B108" s="6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>436</v>
+        <v>190</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>439</v>
+        <v>468</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="8"/>
       <c r="B109" s="6" t="s">
-        <v>163</v>
+        <v>467</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="8"/>
+      <c r="A110" s="8" t="s">
+        <v>278</v>
+      </c>
       <c r="B110" s="6" t="s">
-        <v>495</v>
+        <v>157</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>497</v>
+        <v>341</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>365</v>
+        <v>340</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>364</v>
+        <v>339</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="8" t="s">
-        <v>292</v>
-      </c>
+      <c r="A113" s="8"/>
       <c r="B113" s="6" t="s">
-        <v>167</v>
+        <v>456</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>208</v>
+        <v>414</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>363</v>
+        <v>413</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="8"/>
+      <c r="A114" s="8" t="s">
+        <v>281</v>
+      </c>
       <c r="B114" s="6" t="s">
-        <v>482</v>
+        <v>158</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>438</v>
+        <v>200</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>210</v>
+        <v>412</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="8" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>436</v>
+        <v>201</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>435</v>
+        <v>338</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="8" t="s">
-        <v>294</v>
-      </c>
+      <c r="A116" s="8"/>
       <c r="B116" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>212</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="D116" s="6"/>
       <c r="E116" s="6" t="s">
-        <v>362</v>
+        <v>164</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="8"/>
       <c r="B117" s="6" t="s">
-        <v>169</v>
+        <v>283</v>
       </c>
       <c r="C117" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D117" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D117" s="6"/>
       <c r="E117" s="6" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="8"/>
+      <c r="A118" s="8" t="s">
+        <v>284</v>
+      </c>
       <c r="B118" s="6" t="s">
-        <v>295</v>
+        <v>163</v>
       </c>
       <c r="C118" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D118" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D118" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="E118" s="6" t="s">
-        <v>172</v>
+        <v>337</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="8" t="s">
-        <v>296</v>
-      </c>
+      <c r="A119" s="8"/>
       <c r="B119" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>61</v>
+        <v>330</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>361</v>
+        <v>336</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="8"/>
       <c r="B120" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>351</v>
+        <v>131</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>360</v>
+        <v>451</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="8"/>
       <c r="B121" s="6" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>74</v>
+        <v>453</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>138</v>
+        <v>454</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="8"/>
       <c r="B122" s="6" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>478</v>
+        <v>171</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="8"/>
       <c r="B123" s="6" t="s">
-        <v>179</v>
+        <v>497</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>178</v>
+        <v>508</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>479</v>
+        <v>513</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="8"/>
+      <c r="A124" s="8" t="s">
+        <v>285</v>
+      </c>
       <c r="B124" s="6" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>480</v>
+        <v>117</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="8" t="s">
-        <v>297</v>
-      </c>
+      <c r="A125" s="8"/>
       <c r="B125" s="6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>123</v>
+        <v>505</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>184</v>
+        <v>508</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="8"/>
       <c r="B126" s="6" t="s">
-        <v>183</v>
+        <v>408</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>185</v>
+        <v>409</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>182</v>
+        <v>410</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="8"/>
       <c r="B127" s="6" t="s">
-        <v>432</v>
+        <v>176</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="D127" s="6" t="s">
-        <v>66</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="D127" s="6"/>
       <c r="E127" s="6" t="s">
-        <v>434</v>
+        <v>499</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="8"/>
+      <c r="A128" s="8" t="s">
+        <v>286</v>
+      </c>
       <c r="B128" s="6" t="s">
-        <v>186</v>
+        <v>335</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D128" s="6"/>
+        <v>506</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="E128" s="6" t="s">
-        <v>359</v>
+        <v>507</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="8" t="s">
-        <v>298</v>
-      </c>
+      <c r="A129" s="8"/>
       <c r="B129" s="6" t="s">
-        <v>356</v>
+        <v>202</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>357</v>
+        <v>205</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>358</v>
+        <v>407</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="8"/>
+      <c r="A130" s="8" t="s">
+        <v>287</v>
+      </c>
       <c r="B130" s="6" t="s">
-        <v>213</v>
+        <v>490</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>216</v>
+        <v>333</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>59</v>
+        <v>334</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>431</v>
+        <v>489</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="8" t="s">
-        <v>299</v>
-      </c>
+      <c r="A131" s="8"/>
       <c r="B131" s="6" t="s">
-        <v>518</v>
+        <v>203</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>354</v>
+        <v>205</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>355</v>
+        <v>103</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>517</v>
+        <v>332</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="8"/>
       <c r="B132" s="6" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>109</v>
+        <v>206</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5601,72 +5593,57 @@
         <v>216</v>
       </c>
       <c r="D133" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E133" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="E133" s="6" t="s">
-        <v>352</v>
-      </c>
     </row>
     <row r="134" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="8"/>
+      <c r="A134" s="8" t="s">
+        <v>222</v>
+      </c>
       <c r="B134" s="6" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>227</v>
+        <v>74</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>65</v>
+        <v>330</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>228</v>
+        <v>329</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
-        <v>233</v>
+        <v>482</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>232</v>
+        <v>480</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>351</v>
+        <v>184</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>350</v>
+        <v>481</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="8" t="s">
-        <v>510</v>
-      </c>
+      <c r="A136" s="6"/>
       <c r="B136" s="6" t="s">
-        <v>508</v>
+        <v>485</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="D136" s="6" t="s">
-        <v>195</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="D136" s="6"/>
       <c r="E136" s="6" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="D137" s="6"/>
-      <c r="E137" s="6" t="s">
-        <v>514</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
